--- a/画面設計書/画面設計書_ユーザー管理画面.xlsx
+++ b/画面設計書/画面設計書_ユーザー管理画面.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\OPENMEDIAVAULT\share\file_management_system\＠成果物\画面設計書\ユーザー\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FileManagementSystem_Doc\画面設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31387914-E384-4F1F-A51F-12B3CFA17530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E6406C6-20AC-413F-B500-14E11F4CA77D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="14016" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="10" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="エラーチェック" sheetId="21" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">イベント処理!$A$1:$AN$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">イベント処理!$A$1:$AN$45</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">エラーチェック!$A$1:$AX$9</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">画面詳細!$A$1:$BF$62</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">更新履歴!$A$1:$AN$33</definedName>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="126">
   <si>
     <t>No</t>
     <phoneticPr fontId="1"/>
@@ -541,31 +541,6 @@
     </rPh>
     <rPh sb="3" eb="5">
       <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>初期表示、「退職者を含む」ボタン押下後の一覧</t>
-    <rPh sb="0" eb="4">
-      <t>ショキヒョウジ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>タイショク</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>シャ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>フク</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>ゴ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>イチラン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -685,10 +660,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ユーザーAPI.ユーザー情報取得</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>退職フラグ(0)</t>
     <rPh sb="0" eb="2">
       <t>タイショク</t>
@@ -719,19 +690,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>「退職者を含む」ボタン</t>
-    <rPh sb="1" eb="4">
-      <t>タイショクシャ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>フク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>押下</t>
-  </si>
-  <si>
     <t>入力パラメータ</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -769,10 +727,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>all</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>画面詳細</t>
     <rPh sb="0" eb="4">
       <t>ガメンショウサイ</t>
@@ -955,6 +909,72 @@
     </rPh>
     <rPh sb="6" eb="8">
       <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>retirementFlg=1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>retirementFlg=0</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>retirementFlg=-1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>退職フラグ(1)</t>
+    <rPh sb="0" eb="2">
+      <t>タイショク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>初期表示、「現職者のみ」ボタン押下後の一覧</t>
+    <rPh sb="0" eb="4">
+      <t>ショキヒョウジ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ゲンショク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>シャ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーAPI.ユーザー情報リスト取得</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>APIとパラメータの修正</t>
+    <rPh sb="10" eb="12">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>藤原</t>
+    <rPh sb="0" eb="2">
+      <t>フジワラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>退職フラグ(-1)</t>
+    <rPh sb="0" eb="2">
+      <t>タイショク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1796,28 +1816,94 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1829,23 +1915,20 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1858,69 +1941,6 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2419,7 +2439,7 @@
     <row r="8" spans="2:31" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:31" ht="14.1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="J9" s="116" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K9" s="117"/>
       <c r="L9" s="117"/>
@@ -2716,13 +2736,13 @@
       <c r="Q23" s="7"/>
       <c r="R23" s="8" t="str">
         <f>"第"&amp;TEXT(MAX(更新履歴!B4:B24),"#0.0")&amp;"版"</f>
-        <v>第1.5版</v>
+        <v>第1.6版</v>
       </c>
       <c r="S23" s="7"/>
       <c r="T23" s="7"/>
       <c r="U23" s="125">
         <f>MAX(更新履歴!I6:N29)</f>
-        <v>45729</v>
+        <v>46087</v>
       </c>
       <c r="V23" s="125"/>
       <c r="W23" s="125"/>
@@ -2921,575 +2941,585 @@
   <sheetData>
     <row r="1" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="129" t="s">
+      <c r="B2" s="135" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="130"/>
-      <c r="D2" s="130"/>
-      <c r="E2" s="130"/>
-      <c r="F2" s="130"/>
-      <c r="G2" s="130"/>
-      <c r="H2" s="130"/>
+      <c r="C2" s="136"/>
+      <c r="D2" s="136"/>
+      <c r="E2" s="136"/>
+      <c r="F2" s="136"/>
+      <c r="G2" s="136"/>
+      <c r="H2" s="136"/>
     </row>
     <row r="3" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="130"/>
-      <c r="C3" s="130"/>
-      <c r="D3" s="130"/>
-      <c r="E3" s="130"/>
-      <c r="F3" s="130"/>
-      <c r="G3" s="130"/>
-      <c r="H3" s="130"/>
+      <c r="B3" s="136"/>
+      <c r="C3" s="136"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="136"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="136"/>
     </row>
     <row r="4" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="5" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="131" t="s">
+      <c r="B5" s="134" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="131"/>
-      <c r="D5" s="131"/>
-      <c r="E5" s="131"/>
-      <c r="F5" s="131"/>
-      <c r="G5" s="131"/>
-      <c r="H5" s="131"/>
-      <c r="I5" s="131" t="s">
+      <c r="C5" s="134"/>
+      <c r="D5" s="134"/>
+      <c r="E5" s="134"/>
+      <c r="F5" s="134"/>
+      <c r="G5" s="134"/>
+      <c r="H5" s="134"/>
+      <c r="I5" s="134" t="s">
         <v>5</v>
       </c>
-      <c r="J5" s="131"/>
-      <c r="K5" s="131"/>
-      <c r="L5" s="131"/>
-      <c r="M5" s="131"/>
-      <c r="N5" s="131"/>
-      <c r="O5" s="131" t="s">
+      <c r="J5" s="134"/>
+      <c r="K5" s="134"/>
+      <c r="L5" s="134"/>
+      <c r="M5" s="134"/>
+      <c r="N5" s="134"/>
+      <c r="O5" s="134" t="s">
         <v>10</v>
       </c>
-      <c r="P5" s="131"/>
-      <c r="Q5" s="131"/>
-      <c r="R5" s="131"/>
-      <c r="S5" s="131"/>
-      <c r="T5" s="131" t="s">
+      <c r="P5" s="134"/>
+      <c r="Q5" s="134"/>
+      <c r="R5" s="134"/>
+      <c r="S5" s="134"/>
+      <c r="T5" s="134" t="s">
         <v>6</v>
       </c>
-      <c r="U5" s="131"/>
-      <c r="V5" s="131"/>
-      <c r="W5" s="131"/>
-      <c r="X5" s="131"/>
-      <c r="Y5" s="131"/>
-      <c r="Z5" s="131"/>
-      <c r="AA5" s="131"/>
-      <c r="AB5" s="131"/>
-      <c r="AC5" s="131"/>
-      <c r="AD5" s="131"/>
-      <c r="AE5" s="131"/>
-      <c r="AF5" s="131"/>
-      <c r="AG5" s="131"/>
-      <c r="AH5" s="131" t="s">
+      <c r="U5" s="134"/>
+      <c r="V5" s="134"/>
+      <c r="W5" s="134"/>
+      <c r="X5" s="134"/>
+      <c r="Y5" s="134"/>
+      <c r="Z5" s="134"/>
+      <c r="AA5" s="134"/>
+      <c r="AB5" s="134"/>
+      <c r="AC5" s="134"/>
+      <c r="AD5" s="134"/>
+      <c r="AE5" s="134"/>
+      <c r="AF5" s="134"/>
+      <c r="AG5" s="134"/>
+      <c r="AH5" s="134" t="s">
         <v>7</v>
       </c>
-      <c r="AI5" s="131"/>
-      <c r="AJ5" s="131"/>
-      <c r="AK5" s="131"/>
-      <c r="AL5" s="131"/>
-      <c r="AM5" s="131"/>
+      <c r="AI5" s="134"/>
+      <c r="AJ5" s="134"/>
+      <c r="AK5" s="134"/>
+      <c r="AL5" s="134"/>
+      <c r="AM5" s="134"/>
     </row>
     <row r="6" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="132">
+      <c r="B6" s="133">
         <v>1</v>
       </c>
-      <c r="C6" s="132"/>
-      <c r="D6" s="132"/>
-      <c r="E6" s="132"/>
-      <c r="F6" s="132"/>
-      <c r="G6" s="132"/>
-      <c r="H6" s="132"/>
-      <c r="I6" s="133">
+      <c r="C6" s="133"/>
+      <c r="D6" s="133"/>
+      <c r="E6" s="133"/>
+      <c r="F6" s="133"/>
+      <c r="G6" s="133"/>
+      <c r="H6" s="133"/>
+      <c r="I6" s="130">
         <v>45630</v>
       </c>
-      <c r="J6" s="134"/>
-      <c r="K6" s="134"/>
-      <c r="L6" s="134"/>
-      <c r="M6" s="134"/>
-      <c r="N6" s="134"/>
-      <c r="O6" s="135" t="s">
+      <c r="J6" s="131"/>
+      <c r="K6" s="131"/>
+      <c r="L6" s="131"/>
+      <c r="M6" s="131"/>
+      <c r="N6" s="131"/>
+      <c r="O6" s="132" t="s">
         <v>29</v>
       </c>
-      <c r="P6" s="135"/>
-      <c r="Q6" s="135"/>
-      <c r="R6" s="135"/>
-      <c r="S6" s="135"/>
-      <c r="T6" s="135" t="s">
+      <c r="P6" s="132"/>
+      <c r="Q6" s="132"/>
+      <c r="R6" s="132"/>
+      <c r="S6" s="132"/>
+      <c r="T6" s="132" t="s">
         <v>30</v>
       </c>
-      <c r="U6" s="135"/>
-      <c r="V6" s="135"/>
-      <c r="W6" s="135"/>
-      <c r="X6" s="135"/>
-      <c r="Y6" s="135"/>
-      <c r="Z6" s="135"/>
-      <c r="AA6" s="135"/>
-      <c r="AB6" s="135"/>
-      <c r="AC6" s="135"/>
-      <c r="AD6" s="135"/>
-      <c r="AE6" s="135"/>
-      <c r="AF6" s="135"/>
-      <c r="AG6" s="135"/>
-      <c r="AH6" s="135" t="s">
+      <c r="U6" s="132"/>
+      <c r="V6" s="132"/>
+      <c r="W6" s="132"/>
+      <c r="X6" s="132"/>
+      <c r="Y6" s="132"/>
+      <c r="Z6" s="132"/>
+      <c r="AA6" s="132"/>
+      <c r="AB6" s="132"/>
+      <c r="AC6" s="132"/>
+      <c r="AD6" s="132"/>
+      <c r="AE6" s="132"/>
+      <c r="AF6" s="132"/>
+      <c r="AG6" s="132"/>
+      <c r="AH6" s="132" t="s">
         <v>67</v>
       </c>
-      <c r="AI6" s="135"/>
-      <c r="AJ6" s="135"/>
-      <c r="AK6" s="135"/>
-      <c r="AL6" s="135"/>
-      <c r="AM6" s="135"/>
+      <c r="AI6" s="132"/>
+      <c r="AJ6" s="132"/>
+      <c r="AK6" s="132"/>
+      <c r="AL6" s="132"/>
+      <c r="AM6" s="132"/>
     </row>
     <row r="7" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="132">
+      <c r="B7" s="133">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C7" s="132"/>
-      <c r="D7" s="132"/>
-      <c r="E7" s="132"/>
-      <c r="F7" s="132"/>
-      <c r="G7" s="132"/>
-      <c r="H7" s="132"/>
-      <c r="I7" s="133">
+      <c r="C7" s="133"/>
+      <c r="D7" s="133"/>
+      <c r="E7" s="133"/>
+      <c r="F7" s="133"/>
+      <c r="G7" s="133"/>
+      <c r="H7" s="133"/>
+      <c r="I7" s="130">
         <v>45643</v>
       </c>
-      <c r="J7" s="134"/>
-      <c r="K7" s="134"/>
-      <c r="L7" s="134"/>
-      <c r="M7" s="134"/>
-      <c r="N7" s="134"/>
-      <c r="O7" s="135" t="s">
-        <v>104</v>
-      </c>
-      <c r="P7" s="135"/>
-      <c r="Q7" s="135"/>
-      <c r="R7" s="135"/>
-      <c r="S7" s="135"/>
-      <c r="T7" s="135" t="s">
-        <v>105</v>
-      </c>
-      <c r="U7" s="135"/>
-      <c r="V7" s="135"/>
-      <c r="W7" s="135"/>
-      <c r="X7" s="135"/>
-      <c r="Y7" s="135"/>
-      <c r="Z7" s="135"/>
-      <c r="AA7" s="135"/>
-      <c r="AB7" s="135"/>
-      <c r="AC7" s="135"/>
-      <c r="AD7" s="135"/>
-      <c r="AE7" s="135"/>
-      <c r="AF7" s="135"/>
-      <c r="AG7" s="135"/>
-      <c r="AH7" s="135" t="s">
-        <v>106</v>
-      </c>
-      <c r="AI7" s="135"/>
-      <c r="AJ7" s="135"/>
-      <c r="AK7" s="135"/>
-      <c r="AL7" s="135"/>
-      <c r="AM7" s="135"/>
+      <c r="J7" s="131"/>
+      <c r="K7" s="131"/>
+      <c r="L7" s="131"/>
+      <c r="M7" s="131"/>
+      <c r="N7" s="131"/>
+      <c r="O7" s="132" t="s">
+        <v>99</v>
+      </c>
+      <c r="P7" s="132"/>
+      <c r="Q7" s="132"/>
+      <c r="R7" s="132"/>
+      <c r="S7" s="132"/>
+      <c r="T7" s="132" t="s">
+        <v>100</v>
+      </c>
+      <c r="U7" s="132"/>
+      <c r="V7" s="132"/>
+      <c r="W7" s="132"/>
+      <c r="X7" s="132"/>
+      <c r="Y7" s="132"/>
+      <c r="Z7" s="132"/>
+      <c r="AA7" s="132"/>
+      <c r="AB7" s="132"/>
+      <c r="AC7" s="132"/>
+      <c r="AD7" s="132"/>
+      <c r="AE7" s="132"/>
+      <c r="AF7" s="132"/>
+      <c r="AG7" s="132"/>
+      <c r="AH7" s="132" t="s">
+        <v>101</v>
+      </c>
+      <c r="AI7" s="132"/>
+      <c r="AJ7" s="132"/>
+      <c r="AK7" s="132"/>
+      <c r="AL7" s="132"/>
+      <c r="AM7" s="132"/>
     </row>
     <row r="8" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="132">
+      <c r="B8" s="133">
         <v>1.2</v>
       </c>
-      <c r="C8" s="132"/>
-      <c r="D8" s="132"/>
-      <c r="E8" s="132"/>
-      <c r="F8" s="132"/>
-      <c r="G8" s="132"/>
-      <c r="H8" s="132"/>
-      <c r="I8" s="133">
+      <c r="C8" s="133"/>
+      <c r="D8" s="133"/>
+      <c r="E8" s="133"/>
+      <c r="F8" s="133"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="133"/>
+      <c r="I8" s="130">
         <v>45644</v>
       </c>
-      <c r="J8" s="134"/>
-      <c r="K8" s="134"/>
-      <c r="L8" s="134"/>
-      <c r="M8" s="134"/>
-      <c r="N8" s="134"/>
-      <c r="O8" s="135" t="s">
+      <c r="J8" s="131"/>
+      <c r="K8" s="131"/>
+      <c r="L8" s="131"/>
+      <c r="M8" s="131"/>
+      <c r="N8" s="131"/>
+      <c r="O8" s="132" t="s">
         <v>29</v>
       </c>
-      <c r="P8" s="135"/>
-      <c r="Q8" s="135"/>
-      <c r="R8" s="135"/>
-      <c r="S8" s="135"/>
-      <c r="T8" s="135" t="s">
+      <c r="P8" s="132"/>
+      <c r="Q8" s="132"/>
+      <c r="R8" s="132"/>
+      <c r="S8" s="132"/>
+      <c r="T8" s="132" t="s">
+        <v>102</v>
+      </c>
+      <c r="U8" s="132"/>
+      <c r="V8" s="132"/>
+      <c r="W8" s="132"/>
+      <c r="X8" s="132"/>
+      <c r="Y8" s="132"/>
+      <c r="Z8" s="132"/>
+      <c r="AA8" s="132"/>
+      <c r="AB8" s="132"/>
+      <c r="AC8" s="132"/>
+      <c r="AD8" s="132"/>
+      <c r="AE8" s="132"/>
+      <c r="AF8" s="132"/>
+      <c r="AG8" s="132"/>
+      <c r="AH8" s="132" t="s">
+        <v>67</v>
+      </c>
+      <c r="AI8" s="132"/>
+      <c r="AJ8" s="132"/>
+      <c r="AK8" s="132"/>
+      <c r="AL8" s="132"/>
+      <c r="AM8" s="132"/>
+    </row>
+    <row r="9" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="133">
+        <v>1.3</v>
+      </c>
+      <c r="C9" s="133"/>
+      <c r="D9" s="133"/>
+      <c r="E9" s="133"/>
+      <c r="F9" s="133"/>
+      <c r="G9" s="133"/>
+      <c r="H9" s="133"/>
+      <c r="I9" s="130">
+        <v>45706</v>
+      </c>
+      <c r="J9" s="131"/>
+      <c r="K9" s="131"/>
+      <c r="L9" s="131"/>
+      <c r="M9" s="131"/>
+      <c r="N9" s="131"/>
+      <c r="O9" s="132" t="s">
+        <v>25</v>
+      </c>
+      <c r="P9" s="132"/>
+      <c r="Q9" s="132"/>
+      <c r="R9" s="132"/>
+      <c r="S9" s="132"/>
+      <c r="T9" s="132" t="s">
         <v>107</v>
       </c>
-      <c r="U8" s="135"/>
-      <c r="V8" s="135"/>
-      <c r="W8" s="135"/>
-      <c r="X8" s="135"/>
-      <c r="Y8" s="135"/>
-      <c r="Z8" s="135"/>
-      <c r="AA8" s="135"/>
-      <c r="AB8" s="135"/>
-      <c r="AC8" s="135"/>
-      <c r="AD8" s="135"/>
-      <c r="AE8" s="135"/>
-      <c r="AF8" s="135"/>
-      <c r="AG8" s="135"/>
-      <c r="AH8" s="135" t="s">
-        <v>67</v>
-      </c>
-      <c r="AI8" s="135"/>
-      <c r="AJ8" s="135"/>
-      <c r="AK8" s="135"/>
-      <c r="AL8" s="135"/>
-      <c r="AM8" s="135"/>
-    </row>
-    <row r="9" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="132">
-        <v>1.3</v>
-      </c>
-      <c r="C9" s="132"/>
-      <c r="D9" s="132"/>
-      <c r="E9" s="132"/>
-      <c r="F9" s="132"/>
-      <c r="G9" s="132"/>
-      <c r="H9" s="132"/>
-      <c r="I9" s="133">
-        <v>45706</v>
-      </c>
-      <c r="J9" s="134"/>
-      <c r="K9" s="134"/>
-      <c r="L9" s="134"/>
-      <c r="M9" s="134"/>
-      <c r="N9" s="134"/>
-      <c r="O9" s="135" t="s">
+      <c r="U9" s="132"/>
+      <c r="V9" s="132"/>
+      <c r="W9" s="132"/>
+      <c r="X9" s="132"/>
+      <c r="Y9" s="132"/>
+      <c r="Z9" s="132"/>
+      <c r="AA9" s="132"/>
+      <c r="AB9" s="132"/>
+      <c r="AC9" s="132"/>
+      <c r="AD9" s="132"/>
+      <c r="AE9" s="132"/>
+      <c r="AF9" s="132"/>
+      <c r="AG9" s="132"/>
+      <c r="AH9" s="132" t="s">
+        <v>101</v>
+      </c>
+      <c r="AI9" s="132"/>
+      <c r="AJ9" s="132"/>
+      <c r="AK9" s="132"/>
+      <c r="AL9" s="132"/>
+      <c r="AM9" s="132"/>
+    </row>
+    <row r="10" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B10" s="133">
+        <v>1.4</v>
+      </c>
+      <c r="C10" s="133"/>
+      <c r="D10" s="133"/>
+      <c r="E10" s="133"/>
+      <c r="F10" s="133"/>
+      <c r="G10" s="133"/>
+      <c r="H10" s="133"/>
+      <c r="I10" s="130">
+        <v>45708</v>
+      </c>
+      <c r="J10" s="131"/>
+      <c r="K10" s="131"/>
+      <c r="L10" s="131"/>
+      <c r="M10" s="131"/>
+      <c r="N10" s="131"/>
+      <c r="O10" s="132" t="s">
+        <v>99</v>
+      </c>
+      <c r="P10" s="132"/>
+      <c r="Q10" s="132"/>
+      <c r="R10" s="132"/>
+      <c r="S10" s="132"/>
+      <c r="T10" s="132" t="s">
+        <v>108</v>
+      </c>
+      <c r="U10" s="132"/>
+      <c r="V10" s="132"/>
+      <c r="W10" s="132"/>
+      <c r="X10" s="132"/>
+      <c r="Y10" s="132"/>
+      <c r="Z10" s="132"/>
+      <c r="AA10" s="132"/>
+      <c r="AB10" s="132"/>
+      <c r="AC10" s="132"/>
+      <c r="AD10" s="132"/>
+      <c r="AE10" s="132"/>
+      <c r="AF10" s="132"/>
+      <c r="AG10" s="132"/>
+      <c r="AH10" s="132" t="s">
+        <v>101</v>
+      </c>
+      <c r="AI10" s="132"/>
+      <c r="AJ10" s="132"/>
+      <c r="AK10" s="132"/>
+      <c r="AL10" s="132"/>
+      <c r="AM10" s="132"/>
+    </row>
+    <row r="11" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="133">
+        <v>1.5</v>
+      </c>
+      <c r="C11" s="133"/>
+      <c r="D11" s="133"/>
+      <c r="E11" s="133"/>
+      <c r="F11" s="133"/>
+      <c r="G11" s="133"/>
+      <c r="H11" s="133"/>
+      <c r="I11" s="130">
+        <v>45729</v>
+      </c>
+      <c r="J11" s="131"/>
+      <c r="K11" s="131"/>
+      <c r="L11" s="131"/>
+      <c r="M11" s="131"/>
+      <c r="N11" s="131"/>
+      <c r="O11" s="132" t="s">
+        <v>99</v>
+      </c>
+      <c r="P11" s="132"/>
+      <c r="Q11" s="132"/>
+      <c r="R11" s="132"/>
+      <c r="S11" s="132"/>
+      <c r="T11" s="132" t="s">
+        <v>115</v>
+      </c>
+      <c r="U11" s="132"/>
+      <c r="V11" s="132"/>
+      <c r="W11" s="132"/>
+      <c r="X11" s="132"/>
+      <c r="Y11" s="132"/>
+      <c r="Z11" s="132"/>
+      <c r="AA11" s="132"/>
+      <c r="AB11" s="132"/>
+      <c r="AC11" s="132"/>
+      <c r="AD11" s="132"/>
+      <c r="AE11" s="132"/>
+      <c r="AF11" s="132"/>
+      <c r="AG11" s="132"/>
+      <c r="AH11" s="132" t="s">
+        <v>101</v>
+      </c>
+      <c r="AI11" s="132"/>
+      <c r="AJ11" s="132"/>
+      <c r="AK11" s="132"/>
+      <c r="AL11" s="132"/>
+      <c r="AM11" s="132"/>
+    </row>
+    <row r="12" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B12" s="133">
+        <v>1.6</v>
+      </c>
+      <c r="C12" s="133"/>
+      <c r="D12" s="133"/>
+      <c r="E12" s="133"/>
+      <c r="F12" s="133"/>
+      <c r="G12" s="133"/>
+      <c r="H12" s="133"/>
+      <c r="I12" s="130">
+        <v>46087</v>
+      </c>
+      <c r="J12" s="131"/>
+      <c r="K12" s="131"/>
+      <c r="L12" s="131"/>
+      <c r="M12" s="131"/>
+      <c r="N12" s="131"/>
+      <c r="O12" s="132" t="s">
         <v>25</v>
       </c>
-      <c r="P9" s="135"/>
-      <c r="Q9" s="135"/>
-      <c r="R9" s="135"/>
-      <c r="S9" s="135"/>
-      <c r="T9" s="135" t="s">
-        <v>112</v>
-      </c>
-      <c r="U9" s="135"/>
-      <c r="V9" s="135"/>
-      <c r="W9" s="135"/>
-      <c r="X9" s="135"/>
-      <c r="Y9" s="135"/>
-      <c r="Z9" s="135"/>
-      <c r="AA9" s="135"/>
-      <c r="AB9" s="135"/>
-      <c r="AC9" s="135"/>
-      <c r="AD9" s="135"/>
-      <c r="AE9" s="135"/>
-      <c r="AF9" s="135"/>
-      <c r="AG9" s="135"/>
-      <c r="AH9" s="135" t="s">
-        <v>106</v>
-      </c>
-      <c r="AI9" s="135"/>
-      <c r="AJ9" s="135"/>
-      <c r="AK9" s="135"/>
-      <c r="AL9" s="135"/>
-      <c r="AM9" s="135"/>
-    </row>
-    <row r="10" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="132">
-        <v>1.4</v>
-      </c>
-      <c r="C10" s="132"/>
-      <c r="D10" s="132"/>
-      <c r="E10" s="132"/>
-      <c r="F10" s="132"/>
-      <c r="G10" s="132"/>
-      <c r="H10" s="132"/>
-      <c r="I10" s="133">
-        <v>45708</v>
-      </c>
-      <c r="J10" s="134"/>
-      <c r="K10" s="134"/>
-      <c r="L10" s="134"/>
-      <c r="M10" s="134"/>
-      <c r="N10" s="134"/>
-      <c r="O10" s="135" t="s">
-        <v>104</v>
-      </c>
-      <c r="P10" s="135"/>
-      <c r="Q10" s="135"/>
-      <c r="R10" s="135"/>
-      <c r="S10" s="135"/>
-      <c r="T10" s="135" t="s">
-        <v>113</v>
-      </c>
-      <c r="U10" s="135"/>
-      <c r="V10" s="135"/>
-      <c r="W10" s="135"/>
-      <c r="X10" s="135"/>
-      <c r="Y10" s="135"/>
-      <c r="Z10" s="135"/>
-      <c r="AA10" s="135"/>
-      <c r="AB10" s="135"/>
-      <c r="AC10" s="135"/>
-      <c r="AD10" s="135"/>
-      <c r="AE10" s="135"/>
-      <c r="AF10" s="135"/>
-      <c r="AG10" s="135"/>
-      <c r="AH10" s="135" t="s">
-        <v>106</v>
-      </c>
-      <c r="AI10" s="135"/>
-      <c r="AJ10" s="135"/>
-      <c r="AK10" s="135"/>
-      <c r="AL10" s="135"/>
-      <c r="AM10" s="135"/>
-    </row>
-    <row r="11" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="132">
-        <v>1.5</v>
-      </c>
-      <c r="C11" s="132"/>
-      <c r="D11" s="132"/>
-      <c r="E11" s="132"/>
-      <c r="F11" s="132"/>
-      <c r="G11" s="132"/>
-      <c r="H11" s="132"/>
-      <c r="I11" s="133">
-        <v>45729</v>
-      </c>
-      <c r="J11" s="134"/>
-      <c r="K11" s="134"/>
-      <c r="L11" s="134"/>
-      <c r="M11" s="134"/>
-      <c r="N11" s="134"/>
-      <c r="O11" s="135" t="s">
-        <v>104</v>
-      </c>
-      <c r="P11" s="135"/>
-      <c r="Q11" s="135"/>
-      <c r="R11" s="135"/>
-      <c r="S11" s="135"/>
-      <c r="T11" s="135" t="s">
-        <v>120</v>
-      </c>
-      <c r="U11" s="135"/>
-      <c r="V11" s="135"/>
-      <c r="W11" s="135"/>
-      <c r="X11" s="135"/>
-      <c r="Y11" s="135"/>
-      <c r="Z11" s="135"/>
-      <c r="AA11" s="135"/>
-      <c r="AB11" s="135"/>
-      <c r="AC11" s="135"/>
-      <c r="AD11" s="135"/>
-      <c r="AE11" s="135"/>
-      <c r="AF11" s="135"/>
-      <c r="AG11" s="135"/>
-      <c r="AH11" s="135" t="s">
-        <v>106</v>
-      </c>
-      <c r="AI11" s="135"/>
-      <c r="AJ11" s="135"/>
-      <c r="AK11" s="135"/>
-      <c r="AL11" s="135"/>
-      <c r="AM11" s="135"/>
-    </row>
-    <row r="12" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="136"/>
-      <c r="C12" s="136"/>
-      <c r="D12" s="136"/>
-      <c r="E12" s="136"/>
-      <c r="F12" s="136"/>
-      <c r="G12" s="136"/>
-      <c r="H12" s="136"/>
-      <c r="I12" s="133"/>
-      <c r="J12" s="134"/>
-      <c r="K12" s="134"/>
-      <c r="L12" s="134"/>
-      <c r="M12" s="134"/>
-      <c r="N12" s="134"/>
-      <c r="O12" s="135"/>
-      <c r="P12" s="135"/>
-      <c r="Q12" s="135"/>
-      <c r="R12" s="135"/>
-      <c r="S12" s="135"/>
-      <c r="T12" s="135"/>
-      <c r="U12" s="135"/>
-      <c r="V12" s="135"/>
-      <c r="W12" s="135"/>
-      <c r="X12" s="135"/>
-      <c r="Y12" s="135"/>
-      <c r="Z12" s="135"/>
-      <c r="AA12" s="135"/>
-      <c r="AB12" s="135"/>
-      <c r="AC12" s="135"/>
-      <c r="AD12" s="135"/>
-      <c r="AE12" s="135"/>
-      <c r="AF12" s="135"/>
-      <c r="AG12" s="135"/>
-      <c r="AH12" s="135"/>
-      <c r="AI12" s="135"/>
-      <c r="AJ12" s="135"/>
-      <c r="AK12" s="135"/>
-      <c r="AL12" s="135"/>
-      <c r="AM12" s="135"/>
+      <c r="P12" s="132"/>
+      <c r="Q12" s="132"/>
+      <c r="R12" s="132"/>
+      <c r="S12" s="132"/>
+      <c r="T12" s="132" t="s">
+        <v>123</v>
+      </c>
+      <c r="U12" s="132"/>
+      <c r="V12" s="132"/>
+      <c r="W12" s="132"/>
+      <c r="X12" s="132"/>
+      <c r="Y12" s="132"/>
+      <c r="Z12" s="132"/>
+      <c r="AA12" s="132"/>
+      <c r="AB12" s="132"/>
+      <c r="AC12" s="132"/>
+      <c r="AD12" s="132"/>
+      <c r="AE12" s="132"/>
+      <c r="AF12" s="132"/>
+      <c r="AG12" s="132"/>
+      <c r="AH12" s="132" t="s">
+        <v>124</v>
+      </c>
+      <c r="AI12" s="132"/>
+      <c r="AJ12" s="132"/>
+      <c r="AK12" s="132"/>
+      <c r="AL12" s="132"/>
+      <c r="AM12" s="132"/>
     </row>
     <row r="13" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="136"/>
-      <c r="C13" s="136"/>
-      <c r="D13" s="136"/>
-      <c r="E13" s="136"/>
-      <c r="F13" s="136"/>
-      <c r="G13" s="136"/>
-      <c r="H13" s="136"/>
-      <c r="I13" s="133"/>
-      <c r="J13" s="134"/>
-      <c r="K13" s="134"/>
-      <c r="L13" s="134"/>
-      <c r="M13" s="134"/>
-      <c r="N13" s="134"/>
-      <c r="O13" s="135"/>
-      <c r="P13" s="135"/>
-      <c r="Q13" s="135"/>
-      <c r="R13" s="135"/>
-      <c r="S13" s="135"/>
-      <c r="T13" s="135"/>
-      <c r="U13" s="135"/>
-      <c r="V13" s="135"/>
-      <c r="W13" s="135"/>
-      <c r="X13" s="135"/>
-      <c r="Y13" s="135"/>
-      <c r="Z13" s="135"/>
-      <c r="AA13" s="135"/>
-      <c r="AB13" s="135"/>
-      <c r="AC13" s="135"/>
-      <c r="AD13" s="135"/>
-      <c r="AE13" s="135"/>
-      <c r="AF13" s="135"/>
-      <c r="AG13" s="135"/>
-      <c r="AH13" s="135"/>
-      <c r="AI13" s="135"/>
-      <c r="AJ13" s="135"/>
-      <c r="AK13" s="135"/>
-      <c r="AL13" s="135"/>
-      <c r="AM13" s="135"/>
+      <c r="B13" s="129"/>
+      <c r="C13" s="129"/>
+      <c r="D13" s="129"/>
+      <c r="E13" s="129"/>
+      <c r="F13" s="129"/>
+      <c r="G13" s="129"/>
+      <c r="H13" s="129"/>
+      <c r="I13" s="130"/>
+      <c r="J13" s="131"/>
+      <c r="K13" s="131"/>
+      <c r="L13" s="131"/>
+      <c r="M13" s="131"/>
+      <c r="N13" s="131"/>
+      <c r="O13" s="132"/>
+      <c r="P13" s="132"/>
+      <c r="Q13" s="132"/>
+      <c r="R13" s="132"/>
+      <c r="S13" s="132"/>
+      <c r="T13" s="132"/>
+      <c r="U13" s="132"/>
+      <c r="V13" s="132"/>
+      <c r="W13" s="132"/>
+      <c r="X13" s="132"/>
+      <c r="Y13" s="132"/>
+      <c r="Z13" s="132"/>
+      <c r="AA13" s="132"/>
+      <c r="AB13" s="132"/>
+      <c r="AC13" s="132"/>
+      <c r="AD13" s="132"/>
+      <c r="AE13" s="132"/>
+      <c r="AF13" s="132"/>
+      <c r="AG13" s="132"/>
+      <c r="AH13" s="132"/>
+      <c r="AI13" s="132"/>
+      <c r="AJ13" s="132"/>
+      <c r="AK13" s="132"/>
+      <c r="AL13" s="132"/>
+      <c r="AM13" s="132"/>
     </row>
     <row r="14" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="136"/>
-      <c r="C14" s="136"/>
-      <c r="D14" s="136"/>
-      <c r="E14" s="136"/>
-      <c r="F14" s="136"/>
-      <c r="G14" s="136"/>
-      <c r="H14" s="136"/>
-      <c r="I14" s="133"/>
-      <c r="J14" s="134"/>
-      <c r="K14" s="134"/>
-      <c r="L14" s="134"/>
-      <c r="M14" s="134"/>
-      <c r="N14" s="134"/>
-      <c r="O14" s="135"/>
-      <c r="P14" s="135"/>
-      <c r="Q14" s="135"/>
-      <c r="R14" s="135"/>
-      <c r="S14" s="135"/>
-      <c r="T14" s="135"/>
-      <c r="U14" s="135"/>
-      <c r="V14" s="135"/>
-      <c r="W14" s="135"/>
-      <c r="X14" s="135"/>
-      <c r="Y14" s="135"/>
-      <c r="Z14" s="135"/>
-      <c r="AA14" s="135"/>
-      <c r="AB14" s="135"/>
-      <c r="AC14" s="135"/>
-      <c r="AD14" s="135"/>
-      <c r="AE14" s="135"/>
-      <c r="AF14" s="135"/>
-      <c r="AG14" s="135"/>
-      <c r="AH14" s="135"/>
-      <c r="AI14" s="135"/>
-      <c r="AJ14" s="135"/>
-      <c r="AK14" s="135"/>
-      <c r="AL14" s="135"/>
-      <c r="AM14" s="135"/>
+      <c r="B14" s="129"/>
+      <c r="C14" s="129"/>
+      <c r="D14" s="129"/>
+      <c r="E14" s="129"/>
+      <c r="F14" s="129"/>
+      <c r="G14" s="129"/>
+      <c r="H14" s="129"/>
+      <c r="I14" s="130"/>
+      <c r="J14" s="131"/>
+      <c r="K14" s="131"/>
+      <c r="L14" s="131"/>
+      <c r="M14" s="131"/>
+      <c r="N14" s="131"/>
+      <c r="O14" s="132"/>
+      <c r="P14" s="132"/>
+      <c r="Q14" s="132"/>
+      <c r="R14" s="132"/>
+      <c r="S14" s="132"/>
+      <c r="T14" s="132"/>
+      <c r="U14" s="132"/>
+      <c r="V14" s="132"/>
+      <c r="W14" s="132"/>
+      <c r="X14" s="132"/>
+      <c r="Y14" s="132"/>
+      <c r="Z14" s="132"/>
+      <c r="AA14" s="132"/>
+      <c r="AB14" s="132"/>
+      <c r="AC14" s="132"/>
+      <c r="AD14" s="132"/>
+      <c r="AE14" s="132"/>
+      <c r="AF14" s="132"/>
+      <c r="AG14" s="132"/>
+      <c r="AH14" s="132"/>
+      <c r="AI14" s="132"/>
+      <c r="AJ14" s="132"/>
+      <c r="AK14" s="132"/>
+      <c r="AL14" s="132"/>
+      <c r="AM14" s="132"/>
     </row>
     <row r="15" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="136"/>
-      <c r="C15" s="136"/>
-      <c r="D15" s="136"/>
-      <c r="E15" s="136"/>
-      <c r="F15" s="136"/>
-      <c r="G15" s="136"/>
-      <c r="H15" s="136"/>
-      <c r="I15" s="133"/>
-      <c r="J15" s="134"/>
-      <c r="K15" s="134"/>
-      <c r="L15" s="134"/>
-      <c r="M15" s="134"/>
-      <c r="N15" s="134"/>
-      <c r="O15" s="135"/>
-      <c r="P15" s="135"/>
-      <c r="Q15" s="135"/>
-      <c r="R15" s="135"/>
-      <c r="S15" s="135"/>
-      <c r="T15" s="135"/>
-      <c r="U15" s="135"/>
-      <c r="V15" s="135"/>
-      <c r="W15" s="135"/>
-      <c r="X15" s="135"/>
-      <c r="Y15" s="135"/>
-      <c r="Z15" s="135"/>
-      <c r="AA15" s="135"/>
-      <c r="AB15" s="135"/>
-      <c r="AC15" s="135"/>
-      <c r="AD15" s="135"/>
-      <c r="AE15" s="135"/>
-      <c r="AF15" s="135"/>
-      <c r="AG15" s="135"/>
-      <c r="AH15" s="135"/>
-      <c r="AI15" s="135"/>
-      <c r="AJ15" s="135"/>
-      <c r="AK15" s="135"/>
-      <c r="AL15" s="135"/>
-      <c r="AM15" s="135"/>
+      <c r="B15" s="129"/>
+      <c r="C15" s="129"/>
+      <c r="D15" s="129"/>
+      <c r="E15" s="129"/>
+      <c r="F15" s="129"/>
+      <c r="G15" s="129"/>
+      <c r="H15" s="129"/>
+      <c r="I15" s="130"/>
+      <c r="J15" s="131"/>
+      <c r="K15" s="131"/>
+      <c r="L15" s="131"/>
+      <c r="M15" s="131"/>
+      <c r="N15" s="131"/>
+      <c r="O15" s="132"/>
+      <c r="P15" s="132"/>
+      <c r="Q15" s="132"/>
+      <c r="R15" s="132"/>
+      <c r="S15" s="132"/>
+      <c r="T15" s="132"/>
+      <c r="U15" s="132"/>
+      <c r="V15" s="132"/>
+      <c r="W15" s="132"/>
+      <c r="X15" s="132"/>
+      <c r="Y15" s="132"/>
+      <c r="Z15" s="132"/>
+      <c r="AA15" s="132"/>
+      <c r="AB15" s="132"/>
+      <c r="AC15" s="132"/>
+      <c r="AD15" s="132"/>
+      <c r="AE15" s="132"/>
+      <c r="AF15" s="132"/>
+      <c r="AG15" s="132"/>
+      <c r="AH15" s="132"/>
+      <c r="AI15" s="132"/>
+      <c r="AJ15" s="132"/>
+      <c r="AK15" s="132"/>
+      <c r="AL15" s="132"/>
+      <c r="AM15" s="132"/>
     </row>
     <row r="16" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="136"/>
-      <c r="C16" s="136"/>
-      <c r="D16" s="136"/>
-      <c r="E16" s="136"/>
-      <c r="F16" s="136"/>
-      <c r="G16" s="136"/>
-      <c r="H16" s="136"/>
-      <c r="I16" s="133"/>
-      <c r="J16" s="134"/>
-      <c r="K16" s="134"/>
-      <c r="L16" s="134"/>
-      <c r="M16" s="134"/>
-      <c r="N16" s="134"/>
-      <c r="O16" s="135"/>
-      <c r="P16" s="135"/>
-      <c r="Q16" s="135"/>
-      <c r="R16" s="135"/>
-      <c r="S16" s="135"/>
-      <c r="T16" s="135"/>
-      <c r="U16" s="135"/>
-      <c r="V16" s="135"/>
-      <c r="W16" s="135"/>
-      <c r="X16" s="135"/>
-      <c r="Y16" s="135"/>
-      <c r="Z16" s="135"/>
-      <c r="AA16" s="135"/>
-      <c r="AB16" s="135"/>
-      <c r="AC16" s="135"/>
-      <c r="AD16" s="135"/>
-      <c r="AE16" s="135"/>
-      <c r="AF16" s="135"/>
-      <c r="AG16" s="135"/>
-      <c r="AH16" s="135"/>
-      <c r="AI16" s="135"/>
-      <c r="AJ16" s="135"/>
-      <c r="AK16" s="135"/>
-      <c r="AL16" s="135"/>
-      <c r="AM16" s="135"/>
+      <c r="B16" s="129"/>
+      <c r="C16" s="129"/>
+      <c r="D16" s="129"/>
+      <c r="E16" s="129"/>
+      <c r="F16" s="129"/>
+      <c r="G16" s="129"/>
+      <c r="H16" s="129"/>
+      <c r="I16" s="130"/>
+      <c r="J16" s="131"/>
+      <c r="K16" s="131"/>
+      <c r="L16" s="131"/>
+      <c r="M16" s="131"/>
+      <c r="N16" s="131"/>
+      <c r="O16" s="132"/>
+      <c r="P16" s="132"/>
+      <c r="Q16" s="132"/>
+      <c r="R16" s="132"/>
+      <c r="S16" s="132"/>
+      <c r="T16" s="132"/>
+      <c r="U16" s="132"/>
+      <c r="V16" s="132"/>
+      <c r="W16" s="132"/>
+      <c r="X16" s="132"/>
+      <c r="Y16" s="132"/>
+      <c r="Z16" s="132"/>
+      <c r="AA16" s="132"/>
+      <c r="AB16" s="132"/>
+      <c r="AC16" s="132"/>
+      <c r="AD16" s="132"/>
+      <c r="AE16" s="132"/>
+      <c r="AF16" s="132"/>
+      <c r="AG16" s="132"/>
+      <c r="AH16" s="132"/>
+      <c r="AI16" s="132"/>
+      <c r="AJ16" s="132"/>
+      <c r="AK16" s="132"/>
+      <c r="AL16" s="132"/>
+      <c r="AM16" s="132"/>
     </row>
     <row r="17" spans="2:31" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="J17" s="19"/>
@@ -3675,26 +3705,37 @@
     <row r="33" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="B16:H16"/>
-    <mergeCell ref="I16:N16"/>
-    <mergeCell ref="O16:S16"/>
-    <mergeCell ref="T16:AG16"/>
-    <mergeCell ref="AH16:AM16"/>
-    <mergeCell ref="B15:H15"/>
-    <mergeCell ref="I15:N15"/>
-    <mergeCell ref="O15:S15"/>
-    <mergeCell ref="T15:AG15"/>
-    <mergeCell ref="AH15:AM15"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="I14:N14"/>
-    <mergeCell ref="O14:S14"/>
-    <mergeCell ref="T14:AG14"/>
-    <mergeCell ref="AH14:AM14"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="I13:N13"/>
-    <mergeCell ref="O13:S13"/>
-    <mergeCell ref="T13:AG13"/>
-    <mergeCell ref="AH13:AM13"/>
+    <mergeCell ref="B2:H3"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="I5:N5"/>
+    <mergeCell ref="O5:S5"/>
+    <mergeCell ref="T5:AG5"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="I7:N7"/>
+    <mergeCell ref="O7:S7"/>
+    <mergeCell ref="T7:AG7"/>
+    <mergeCell ref="AH7:AM7"/>
+    <mergeCell ref="AH5:AM5"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="I6:N6"/>
+    <mergeCell ref="O6:S6"/>
+    <mergeCell ref="T6:AG6"/>
+    <mergeCell ref="AH6:AM6"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="I9:N9"/>
+    <mergeCell ref="T8:AG8"/>
+    <mergeCell ref="T9:AG9"/>
+    <mergeCell ref="AH9:AM9"/>
+    <mergeCell ref="O9:S9"/>
+    <mergeCell ref="AH8:AM8"/>
+    <mergeCell ref="O8:S8"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="I8:N8"/>
+    <mergeCell ref="T10:AG10"/>
+    <mergeCell ref="AH10:AM10"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="O10:S10"/>
+    <mergeCell ref="I10:N10"/>
     <mergeCell ref="B12:H12"/>
     <mergeCell ref="I12:N12"/>
     <mergeCell ref="T12:AG12"/>
@@ -3705,37 +3746,26 @@
     <mergeCell ref="I11:N11"/>
     <mergeCell ref="T11:AG11"/>
     <mergeCell ref="AH11:AM11"/>
-    <mergeCell ref="T10:AG10"/>
-    <mergeCell ref="AH10:AM10"/>
-    <mergeCell ref="B10:H10"/>
-    <mergeCell ref="O10:S10"/>
-    <mergeCell ref="I10:N10"/>
-    <mergeCell ref="B9:H9"/>
-    <mergeCell ref="I9:N9"/>
-    <mergeCell ref="T8:AG8"/>
-    <mergeCell ref="T9:AG9"/>
-    <mergeCell ref="AH9:AM9"/>
-    <mergeCell ref="O9:S9"/>
-    <mergeCell ref="AH8:AM8"/>
-    <mergeCell ref="O8:S8"/>
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="I8:N8"/>
-    <mergeCell ref="AH5:AM5"/>
-    <mergeCell ref="B6:H6"/>
-    <mergeCell ref="I6:N6"/>
-    <mergeCell ref="O6:S6"/>
-    <mergeCell ref="T6:AG6"/>
-    <mergeCell ref="AH6:AM6"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="I7:N7"/>
-    <mergeCell ref="O7:S7"/>
-    <mergeCell ref="T7:AG7"/>
-    <mergeCell ref="AH7:AM7"/>
-    <mergeCell ref="B2:H3"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="I5:N5"/>
-    <mergeCell ref="O5:S5"/>
-    <mergeCell ref="T5:AG5"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="I13:N13"/>
+    <mergeCell ref="O13:S13"/>
+    <mergeCell ref="T13:AG13"/>
+    <mergeCell ref="AH13:AM13"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="I14:N14"/>
+    <mergeCell ref="O14:S14"/>
+    <mergeCell ref="T14:AG14"/>
+    <mergeCell ref="AH14:AM14"/>
+    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="I15:N15"/>
+    <mergeCell ref="O15:S15"/>
+    <mergeCell ref="T15:AG15"/>
+    <mergeCell ref="AH15:AM15"/>
+    <mergeCell ref="B16:H16"/>
+    <mergeCell ref="I16:N16"/>
+    <mergeCell ref="O16:S16"/>
+    <mergeCell ref="T16:AG16"/>
+    <mergeCell ref="AH16:AM16"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3757,36 +3787,36 @@
       <c r="A1" s="21"/>
     </row>
     <row r="2" spans="1:40" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="129" t="s">
+      <c r="B2" s="135" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="129"/>
-      <c r="D2" s="129"/>
-      <c r="E2" s="129"/>
-      <c r="F2" s="129"/>
-      <c r="G2" s="129"/>
-      <c r="H2" s="129"/>
-      <c r="I2" s="129"/>
-      <c r="J2" s="129"/>
-      <c r="K2" s="129"/>
-      <c r="L2" s="129"/>
-      <c r="M2" s="129"/>
-      <c r="N2" s="129"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="135"/>
+      <c r="E2" s="135"/>
+      <c r="F2" s="135"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="135"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="135"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="135"/>
+      <c r="M2" s="135"/>
+      <c r="N2" s="135"/>
     </row>
     <row r="3" spans="1:40" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="129"/>
-      <c r="C3" s="129"/>
-      <c r="D3" s="129"/>
-      <c r="E3" s="129"/>
-      <c r="F3" s="129"/>
-      <c r="G3" s="129"/>
-      <c r="H3" s="129"/>
-      <c r="I3" s="129"/>
-      <c r="J3" s="129"/>
-      <c r="K3" s="129"/>
-      <c r="L3" s="129"/>
-      <c r="M3" s="129"/>
-      <c r="N3" s="129"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="135"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="135"/>
+      <c r="H3" s="135"/>
+      <c r="I3" s="135"/>
+      <c r="J3" s="135"/>
+      <c r="K3" s="135"/>
+      <c r="L3" s="135"/>
+      <c r="M3" s="135"/>
+      <c r="N3" s="135"/>
     </row>
     <row r="4" spans="1:40" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="22" t="s">
@@ -3808,7 +3838,7 @@
         <v>71</v>
       </c>
       <c r="AN4" s="62" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:40" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
@@ -3829,7 +3859,7 @@
     <row r="16" spans="1:40" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="17" spans="2:57" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="62" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="2:57" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -3850,18 +3880,18 @@
       </c>
     </row>
     <row r="31" spans="2:57" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B31" s="140" t="s">
+      <c r="B31" s="153" t="s">
         <v>0</v>
       </c>
-      <c r="C31" s="141"/>
-      <c r="D31" s="140" t="s">
+      <c r="C31" s="155"/>
+      <c r="D31" s="153" t="s">
         <v>12</v>
       </c>
-      <c r="E31" s="144"/>
-      <c r="F31" s="144"/>
-      <c r="G31" s="144"/>
-      <c r="H31" s="144"/>
-      <c r="I31" s="141"/>
+      <c r="E31" s="154"/>
+      <c r="F31" s="154"/>
+      <c r="G31" s="154"/>
+      <c r="H31" s="154"/>
+      <c r="I31" s="155"/>
       <c r="J31" s="162" t="s">
         <v>13</v>
       </c>
@@ -3876,133 +3906,133 @@
       <c r="S31" s="163"/>
       <c r="T31" s="163"/>
       <c r="U31" s="164"/>
-      <c r="V31" s="148" t="s">
+      <c r="V31" s="169" t="s">
         <v>37</v>
       </c>
-      <c r="W31" s="146" t="s">
+      <c r="W31" s="167" t="s">
         <v>16</v>
       </c>
-      <c r="X31" s="147"/>
-      <c r="Y31" s="156" t="s">
+      <c r="X31" s="168"/>
+      <c r="Y31" s="141" t="s">
         <v>38</v>
       </c>
-      <c r="Z31" s="165"/>
-      <c r="AA31" s="165"/>
-      <c r="AB31" s="165"/>
-      <c r="AC31" s="157"/>
-      <c r="AD31" s="156" t="s">
+      <c r="Z31" s="142"/>
+      <c r="AA31" s="142"/>
+      <c r="AB31" s="142"/>
+      <c r="AC31" s="143"/>
+      <c r="AD31" s="141" t="s">
         <v>39</v>
       </c>
-      <c r="AE31" s="157"/>
-      <c r="AF31" s="156" t="s">
+      <c r="AE31" s="143"/>
+      <c r="AF31" s="141" t="s">
         <v>40</v>
       </c>
-      <c r="AG31" s="157"/>
-      <c r="AH31" s="150" t="s">
+      <c r="AG31" s="143"/>
+      <c r="AH31" s="147" t="s">
         <v>41</v>
       </c>
-      <c r="AI31" s="154"/>
-      <c r="AJ31" s="151"/>
-      <c r="AK31" s="150" t="s">
+      <c r="AI31" s="151"/>
+      <c r="AJ31" s="148"/>
+      <c r="AK31" s="147" t="s">
         <v>42</v>
       </c>
-      <c r="AL31" s="151"/>
-      <c r="AM31" s="150" t="s">
+      <c r="AL31" s="148"/>
+      <c r="AM31" s="147" t="s">
         <v>43</v>
       </c>
-      <c r="AN31" s="154"/>
-      <c r="AO31" s="154"/>
-      <c r="AP31" s="151"/>
-      <c r="AQ31" s="140" t="s">
+      <c r="AN31" s="151"/>
+      <c r="AO31" s="151"/>
+      <c r="AP31" s="148"/>
+      <c r="AQ31" s="153" t="s">
         <v>15</v>
       </c>
-      <c r="AR31" s="144"/>
-      <c r="AS31" s="144"/>
-      <c r="AT31" s="144"/>
-      <c r="AU31" s="144"/>
-      <c r="AV31" s="144"/>
-      <c r="AW31" s="144"/>
-      <c r="AX31" s="144"/>
-      <c r="AY31" s="144"/>
-      <c r="AZ31" s="144"/>
-      <c r="BA31" s="144"/>
-      <c r="BB31" s="144"/>
-      <c r="BC31" s="144"/>
-      <c r="BD31" s="144"/>
-      <c r="BE31" s="141"/>
+      <c r="AR31" s="154"/>
+      <c r="AS31" s="154"/>
+      <c r="AT31" s="154"/>
+      <c r="AU31" s="154"/>
+      <c r="AV31" s="154"/>
+      <c r="AW31" s="154"/>
+      <c r="AX31" s="154"/>
+      <c r="AY31" s="154"/>
+      <c r="AZ31" s="154"/>
+      <c r="BA31" s="154"/>
+      <c r="BB31" s="154"/>
+      <c r="BC31" s="154"/>
+      <c r="BD31" s="154"/>
+      <c r="BE31" s="155"/>
     </row>
     <row r="32" spans="2:57" ht="13.8" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="142"/>
-      <c r="C32" s="143"/>
-      <c r="D32" s="142"/>
-      <c r="E32" s="145"/>
-      <c r="F32" s="145"/>
-      <c r="G32" s="145"/>
-      <c r="H32" s="145"/>
-      <c r="I32" s="143"/>
-      <c r="J32" s="137" t="s">
+      <c r="B32" s="156"/>
+      <c r="C32" s="158"/>
+      <c r="D32" s="156"/>
+      <c r="E32" s="157"/>
+      <c r="F32" s="157"/>
+      <c r="G32" s="157"/>
+      <c r="H32" s="157"/>
+      <c r="I32" s="158"/>
+      <c r="J32" s="159" t="s">
         <v>14</v>
       </c>
-      <c r="K32" s="138"/>
-      <c r="L32" s="138"/>
-      <c r="M32" s="138"/>
-      <c r="N32" s="138"/>
-      <c r="O32" s="139"/>
-      <c r="P32" s="137" t="s">
+      <c r="K32" s="160"/>
+      <c r="L32" s="160"/>
+      <c r="M32" s="160"/>
+      <c r="N32" s="160"/>
+      <c r="O32" s="161"/>
+      <c r="P32" s="159" t="s">
         <v>24</v>
       </c>
-      <c r="Q32" s="138"/>
-      <c r="R32" s="138"/>
-      <c r="S32" s="138"/>
-      <c r="T32" s="138"/>
-      <c r="U32" s="139"/>
-      <c r="V32" s="149"/>
+      <c r="Q32" s="160"/>
+      <c r="R32" s="160"/>
+      <c r="S32" s="160"/>
+      <c r="T32" s="160"/>
+      <c r="U32" s="161"/>
+      <c r="V32" s="170"/>
       <c r="W32" s="80" t="s">
         <v>18</v>
       </c>
       <c r="X32" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="Y32" s="158"/>
-      <c r="Z32" s="166"/>
-      <c r="AA32" s="166"/>
-      <c r="AB32" s="166"/>
-      <c r="AC32" s="159"/>
-      <c r="AD32" s="158"/>
-      <c r="AE32" s="159"/>
-      <c r="AF32" s="158"/>
-      <c r="AG32" s="159"/>
-      <c r="AH32" s="152"/>
-      <c r="AI32" s="155"/>
-      <c r="AJ32" s="153"/>
-      <c r="AK32" s="152"/>
-      <c r="AL32" s="153"/>
-      <c r="AM32" s="152"/>
-      <c r="AN32" s="155"/>
-      <c r="AO32" s="155"/>
-      <c r="AP32" s="153"/>
-      <c r="AQ32" s="142"/>
-      <c r="AR32" s="145"/>
-      <c r="AS32" s="145"/>
-      <c r="AT32" s="145"/>
-      <c r="AU32" s="145"/>
-      <c r="AV32" s="145"/>
-      <c r="AW32" s="145"/>
-      <c r="AX32" s="145"/>
-      <c r="AY32" s="145"/>
-      <c r="AZ32" s="145"/>
-      <c r="BA32" s="145"/>
-      <c r="BB32" s="145"/>
-      <c r="BC32" s="145"/>
-      <c r="BD32" s="145"/>
-      <c r="BE32" s="143"/>
+      <c r="Y32" s="144"/>
+      <c r="Z32" s="145"/>
+      <c r="AA32" s="145"/>
+      <c r="AB32" s="145"/>
+      <c r="AC32" s="146"/>
+      <c r="AD32" s="144"/>
+      <c r="AE32" s="146"/>
+      <c r="AF32" s="144"/>
+      <c r="AG32" s="146"/>
+      <c r="AH32" s="149"/>
+      <c r="AI32" s="152"/>
+      <c r="AJ32" s="150"/>
+      <c r="AK32" s="149"/>
+      <c r="AL32" s="150"/>
+      <c r="AM32" s="149"/>
+      <c r="AN32" s="152"/>
+      <c r="AO32" s="152"/>
+      <c r="AP32" s="150"/>
+      <c r="AQ32" s="156"/>
+      <c r="AR32" s="157"/>
+      <c r="AS32" s="157"/>
+      <c r="AT32" s="157"/>
+      <c r="AU32" s="157"/>
+      <c r="AV32" s="157"/>
+      <c r="AW32" s="157"/>
+      <c r="AX32" s="157"/>
+      <c r="AY32" s="157"/>
+      <c r="AZ32" s="157"/>
+      <c r="BA32" s="157"/>
+      <c r="BB32" s="157"/>
+      <c r="BC32" s="157"/>
+      <c r="BD32" s="157"/>
+      <c r="BE32" s="158"/>
     </row>
     <row r="33" spans="1:62" s="24" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="26"/>
-      <c r="B33" s="160">
+      <c r="B33" s="139">
         <v>1</v>
       </c>
-      <c r="C33" s="161"/>
+      <c r="C33" s="140"/>
       <c r="D33" s="25" t="s">
         <v>54</v>
       </c>
@@ -4074,76 +4104,76 @@
     </row>
     <row r="34" spans="1:62" s="24" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="26"/>
-      <c r="B34" s="167" t="s">
-        <v>72</v>
-      </c>
-      <c r="C34" s="168"/>
-      <c r="D34" s="168"/>
-      <c r="E34" s="168"/>
-      <c r="F34" s="168"/>
-      <c r="G34" s="168"/>
-      <c r="H34" s="168"/>
-      <c r="I34" s="168"/>
-      <c r="J34" s="168"/>
-      <c r="K34" s="168"/>
-      <c r="L34" s="168"/>
-      <c r="M34" s="168"/>
-      <c r="N34" s="168"/>
-      <c r="O34" s="168"/>
-      <c r="P34" s="168"/>
-      <c r="Q34" s="168"/>
-      <c r="R34" s="168"/>
-      <c r="S34" s="168"/>
-      <c r="T34" s="168"/>
-      <c r="U34" s="168"/>
-      <c r="V34" s="168"/>
-      <c r="W34" s="168"/>
-      <c r="X34" s="168"/>
-      <c r="Y34" s="168"/>
-      <c r="Z34" s="168"/>
-      <c r="AA34" s="168"/>
-      <c r="AB34" s="168"/>
-      <c r="AC34" s="168"/>
-      <c r="AD34" s="168"/>
-      <c r="AE34" s="168"/>
-      <c r="AF34" s="168"/>
-      <c r="AG34" s="168"/>
-      <c r="AH34" s="168"/>
-      <c r="AI34" s="168"/>
-      <c r="AJ34" s="168"/>
-      <c r="AK34" s="168"/>
-      <c r="AL34" s="168"/>
-      <c r="AM34" s="168"/>
-      <c r="AN34" s="168"/>
-      <c r="AO34" s="168"/>
-      <c r="AP34" s="168"/>
-      <c r="AQ34" s="168"/>
-      <c r="AR34" s="168"/>
-      <c r="AS34" s="168"/>
-      <c r="AT34" s="168"/>
-      <c r="AU34" s="168"/>
-      <c r="AV34" s="168"/>
-      <c r="AW34" s="168"/>
-      <c r="AX34" s="168"/>
-      <c r="AY34" s="168"/>
-      <c r="AZ34" s="168"/>
-      <c r="BA34" s="168"/>
-      <c r="BB34" s="168"/>
-      <c r="BC34" s="168"/>
-      <c r="BD34" s="168"/>
-      <c r="BE34" s="168"/>
+      <c r="B34" s="165" t="s">
+        <v>121</v>
+      </c>
+      <c r="C34" s="166"/>
+      <c r="D34" s="166"/>
+      <c r="E34" s="166"/>
+      <c r="F34" s="166"/>
+      <c r="G34" s="166"/>
+      <c r="H34" s="166"/>
+      <c r="I34" s="166"/>
+      <c r="J34" s="166"/>
+      <c r="K34" s="166"/>
+      <c r="L34" s="166"/>
+      <c r="M34" s="166"/>
+      <c r="N34" s="166"/>
+      <c r="O34" s="166"/>
+      <c r="P34" s="166"/>
+      <c r="Q34" s="166"/>
+      <c r="R34" s="166"/>
+      <c r="S34" s="166"/>
+      <c r="T34" s="166"/>
+      <c r="U34" s="166"/>
+      <c r="V34" s="166"/>
+      <c r="W34" s="166"/>
+      <c r="X34" s="166"/>
+      <c r="Y34" s="166"/>
+      <c r="Z34" s="166"/>
+      <c r="AA34" s="166"/>
+      <c r="AB34" s="166"/>
+      <c r="AC34" s="166"/>
+      <c r="AD34" s="166"/>
+      <c r="AE34" s="166"/>
+      <c r="AF34" s="166"/>
+      <c r="AG34" s="166"/>
+      <c r="AH34" s="166"/>
+      <c r="AI34" s="166"/>
+      <c r="AJ34" s="166"/>
+      <c r="AK34" s="166"/>
+      <c r="AL34" s="166"/>
+      <c r="AM34" s="166"/>
+      <c r="AN34" s="166"/>
+      <c r="AO34" s="166"/>
+      <c r="AP34" s="166"/>
+      <c r="AQ34" s="166"/>
+      <c r="AR34" s="166"/>
+      <c r="AS34" s="166"/>
+      <c r="AT34" s="166"/>
+      <c r="AU34" s="166"/>
+      <c r="AV34" s="166"/>
+      <c r="AW34" s="166"/>
+      <c r="AX34" s="166"/>
+      <c r="AY34" s="166"/>
+      <c r="AZ34" s="166"/>
+      <c r="BA34" s="166"/>
+      <c r="BB34" s="166"/>
+      <c r="BC34" s="166"/>
+      <c r="BD34" s="166"/>
+      <c r="BE34" s="166"/>
       <c r="BH34" s="24" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="35" spans="1:62" s="24" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="26"/>
-      <c r="B35" s="160">
+      <c r="B35" s="139">
         <v>2</v>
       </c>
-      <c r="C35" s="161"/>
+      <c r="C35" s="140"/>
       <c r="D35" s="25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E35" s="64"/>
       <c r="F35" s="64"/>
@@ -4207,12 +4237,12 @@
     </row>
     <row r="36" spans="1:62" s="24" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="26"/>
-      <c r="B36" s="160">
+      <c r="B36" s="139">
         <v>3</v>
       </c>
-      <c r="C36" s="161"/>
+      <c r="C36" s="140"/>
       <c r="D36" s="25" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E36" s="64"/>
       <c r="F36" s="64"/>
@@ -4276,10 +4306,10 @@
     </row>
     <row r="37" spans="1:62" s="24" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="26"/>
-      <c r="B37" s="160">
+      <c r="B37" s="139">
         <v>4</v>
       </c>
-      <c r="C37" s="161"/>
+      <c r="C37" s="140"/>
       <c r="D37" s="25" t="s">
         <v>29</v>
       </c>
@@ -4345,10 +4375,10 @@
     </row>
     <row r="38" spans="1:62" s="24" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="26"/>
-      <c r="B38" s="160">
+      <c r="B38" s="139">
         <v>5</v>
       </c>
-      <c r="C38" s="161"/>
+      <c r="C38" s="140"/>
       <c r="D38" s="25" t="s">
         <v>62</v>
       </c>
@@ -4416,10 +4446,10 @@
     </row>
     <row r="39" spans="1:62" s="24" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="26"/>
-      <c r="B39" s="160">
+      <c r="B39" s="139">
         <v>6</v>
       </c>
-      <c r="C39" s="161"/>
+      <c r="C39" s="140"/>
       <c r="D39" s="25" t="s">
         <v>59</v>
       </c>
@@ -4429,7 +4459,7 @@
       <c r="H39" s="64"/>
       <c r="I39" s="65"/>
       <c r="J39" s="25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K39" s="64"/>
       <c r="L39" s="64"/>
@@ -4437,7 +4467,7 @@
       <c r="N39" s="64"/>
       <c r="O39" s="65"/>
       <c r="P39" s="39" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q39" s="64"/>
       <c r="R39" s="64"/>
@@ -4487,12 +4517,12 @@
     </row>
     <row r="40" spans="1:62" s="24" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="26"/>
-      <c r="B40" s="160">
+      <c r="B40" s="139">
         <v>7</v>
       </c>
-      <c r="C40" s="161"/>
+      <c r="C40" s="140"/>
       <c r="D40" s="25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E40" s="64"/>
       <c r="F40" s="64"/>
@@ -4500,7 +4530,7 @@
       <c r="H40" s="64"/>
       <c r="I40" s="65"/>
       <c r="J40" s="25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K40" s="64"/>
       <c r="L40" s="64"/>
@@ -4541,7 +4571,7 @@
       <c r="AO40" s="64"/>
       <c r="AP40" s="65"/>
       <c r="AQ40" s="25" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="AR40" s="64"/>
       <c r="AS40" s="64"/>
@@ -4560,12 +4590,12 @@
     </row>
     <row r="41" spans="1:62" s="24" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="26"/>
-      <c r="B41" s="160">
+      <c r="B41" s="139">
         <v>8</v>
       </c>
-      <c r="C41" s="161"/>
+      <c r="C41" s="140"/>
       <c r="D41" s="25" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E41" s="64"/>
       <c r="F41" s="64"/>
@@ -4573,7 +4603,7 @@
       <c r="H41" s="64"/>
       <c r="I41" s="65"/>
       <c r="J41" s="25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K41" s="64"/>
       <c r="L41" s="64"/>
@@ -4581,7 +4611,7 @@
       <c r="N41" s="64"/>
       <c r="O41" s="65"/>
       <c r="P41" s="39" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q41" s="64"/>
       <c r="R41" s="64"/>
@@ -4614,7 +4644,7 @@
       <c r="AO41" s="64"/>
       <c r="AP41" s="65"/>
       <c r="AQ41" s="25" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="AR41" s="64"/>
       <c r="AS41" s="64"/>
@@ -4633,12 +4663,12 @@
     </row>
     <row r="42" spans="1:62" s="24" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="26"/>
-      <c r="B42" s="160">
+      <c r="B42" s="139">
         <v>9</v>
       </c>
-      <c r="C42" s="161"/>
+      <c r="C42" s="140"/>
       <c r="D42" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E42" s="64"/>
       <c r="F42" s="64"/>
@@ -4646,7 +4676,7 @@
       <c r="H42" s="64"/>
       <c r="I42" s="65"/>
       <c r="J42" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K42" s="64"/>
       <c r="L42" s="64"/>
@@ -4654,7 +4684,7 @@
       <c r="N42" s="64"/>
       <c r="O42" s="65"/>
       <c r="P42" s="39" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q42" s="64"/>
       <c r="R42" s="64"/>
@@ -4687,7 +4717,7 @@
       <c r="AO42" s="64"/>
       <c r="AP42" s="65"/>
       <c r="AQ42" s="25" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="AR42" s="64"/>
       <c r="AS42" s="64"/>
@@ -4706,12 +4736,12 @@
     </row>
     <row r="43" spans="1:62" s="24" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="26"/>
-      <c r="B43" s="160">
+      <c r="B43" s="139">
         <v>10</v>
       </c>
-      <c r="C43" s="161"/>
+      <c r="C43" s="140"/>
       <c r="D43" s="25" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E43" s="64"/>
       <c r="F43" s="64"/>
@@ -4719,7 +4749,7 @@
       <c r="H43" s="64"/>
       <c r="I43" s="65"/>
       <c r="J43" s="25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K43" s="64"/>
       <c r="L43" s="64"/>
@@ -4727,7 +4757,7 @@
       <c r="N43" s="64"/>
       <c r="O43" s="65"/>
       <c r="P43" s="39" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q43" s="64"/>
       <c r="R43" s="64"/>
@@ -4777,10 +4807,10 @@
     </row>
     <row r="44" spans="1:62" s="24" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="26"/>
-      <c r="B44" s="160">
+      <c r="B44" s="139">
         <v>11</v>
       </c>
-      <c r="C44" s="161"/>
+      <c r="C44" s="140"/>
       <c r="D44" s="25" t="s">
         <v>16</v>
       </c>
@@ -4790,7 +4820,7 @@
       <c r="H44" s="64"/>
       <c r="I44" s="65"/>
       <c r="J44" s="25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K44" s="64"/>
       <c r="L44" s="64"/>
@@ -4798,7 +4828,7 @@
       <c r="N44" s="64"/>
       <c r="O44" s="65"/>
       <c r="P44" s="39" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q44" s="64"/>
       <c r="R44" s="64"/>
@@ -4848,12 +4878,12 @@
     </row>
     <row r="45" spans="1:62" s="24" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="26"/>
-      <c r="B45" s="160">
+      <c r="B45" s="139">
         <v>12</v>
       </c>
-      <c r="C45" s="161"/>
+      <c r="C45" s="140"/>
       <c r="D45" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E45" s="64"/>
       <c r="F45" s="64"/>
@@ -4861,7 +4891,7 @@
       <c r="H45" s="64"/>
       <c r="I45" s="65"/>
       <c r="J45" s="25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K45" s="64"/>
       <c r="L45" s="64"/>
@@ -4869,7 +4899,7 @@
       <c r="N45" s="64"/>
       <c r="O45" s="65"/>
       <c r="P45" s="39" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q45" s="64"/>
       <c r="R45" s="64"/>
@@ -4919,10 +4949,10 @@
     </row>
     <row r="46" spans="1:62" s="24" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="26"/>
-      <c r="B46" s="160">
+      <c r="B46" s="139">
         <v>13</v>
       </c>
-      <c r="C46" s="161"/>
+      <c r="C46" s="140"/>
       <c r="D46" s="25" t="s">
         <v>57</v>
       </c>
@@ -4971,7 +5001,7 @@
       <c r="AO46" s="64"/>
       <c r="AP46" s="65"/>
       <c r="AQ46" s="36" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AR46" s="37"/>
       <c r="AS46" s="37"/>
@@ -4990,10 +5020,10 @@
     </row>
     <row r="47" spans="1:62" s="24" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="26"/>
-      <c r="B47" s="160">
+      <c r="B47" s="139">
         <v>14</v>
       </c>
-      <c r="C47" s="161"/>
+      <c r="C47" s="140"/>
       <c r="D47" s="25" t="s">
         <v>58</v>
       </c>
@@ -5065,136 +5095,136 @@
       <c r="O49" s="14"/>
     </row>
     <row r="50" spans="2:57" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="156" t="s">
+      <c r="B50" s="141" t="s">
         <v>0</v>
       </c>
-      <c r="C50" s="157"/>
-      <c r="D50" s="156" t="s">
+      <c r="C50" s="143"/>
+      <c r="D50" s="141" t="s">
         <v>12</v>
       </c>
-      <c r="E50" s="165"/>
-      <c r="F50" s="165"/>
-      <c r="G50" s="165"/>
-      <c r="H50" s="165"/>
-      <c r="I50" s="157"/>
-      <c r="J50" s="156" t="s">
+      <c r="E50" s="142"/>
+      <c r="F50" s="142"/>
+      <c r="G50" s="142"/>
+      <c r="H50" s="142"/>
+      <c r="I50" s="143"/>
+      <c r="J50" s="141" t="s">
         <v>1</v>
       </c>
-      <c r="K50" s="165"/>
-      <c r="L50" s="165"/>
-      <c r="M50" s="165"/>
-      <c r="N50" s="165"/>
-      <c r="O50" s="165"/>
-      <c r="P50" s="157"/>
-      <c r="Q50" s="156" t="s">
+      <c r="K50" s="142"/>
+      <c r="L50" s="142"/>
+      <c r="M50" s="142"/>
+      <c r="N50" s="142"/>
+      <c r="O50" s="142"/>
+      <c r="P50" s="143"/>
+      <c r="Q50" s="141" t="s">
         <v>21</v>
       </c>
-      <c r="R50" s="165"/>
-      <c r="S50" s="165"/>
-      <c r="T50" s="157"/>
-      <c r="U50" s="156" t="s">
+      <c r="R50" s="142"/>
+      <c r="S50" s="142"/>
+      <c r="T50" s="143"/>
+      <c r="U50" s="141" t="s">
         <v>22</v>
       </c>
-      <c r="V50" s="165"/>
-      <c r="W50" s="157"/>
-      <c r="X50" s="156" t="s">
+      <c r="V50" s="142"/>
+      <c r="W50" s="143"/>
+      <c r="X50" s="141" t="s">
         <v>15</v>
       </c>
-      <c r="Y50" s="165"/>
-      <c r="Z50" s="165"/>
-      <c r="AA50" s="165"/>
-      <c r="AB50" s="165"/>
-      <c r="AC50" s="165"/>
-      <c r="AD50" s="165"/>
-      <c r="AE50" s="165"/>
-      <c r="AF50" s="165"/>
-      <c r="AG50" s="165"/>
-      <c r="AH50" s="165"/>
-      <c r="AI50" s="165"/>
-      <c r="AJ50" s="165"/>
-      <c r="AK50" s="165"/>
-      <c r="AL50" s="165"/>
-      <c r="AM50" s="165"/>
-      <c r="AN50" s="165"/>
-      <c r="AO50" s="165"/>
-      <c r="AP50" s="165"/>
-      <c r="AQ50" s="165"/>
-      <c r="AR50" s="165"/>
-      <c r="AS50" s="165"/>
-      <c r="AT50" s="165"/>
-      <c r="AU50" s="165"/>
-      <c r="AV50" s="165"/>
-      <c r="AW50" s="165"/>
-      <c r="AX50" s="165"/>
-      <c r="AY50" s="165"/>
-      <c r="AZ50" s="165"/>
-      <c r="BA50" s="165"/>
-      <c r="BB50" s="165"/>
-      <c r="BC50" s="165"/>
-      <c r="BD50" s="165"/>
-      <c r="BE50" s="157"/>
+      <c r="Y50" s="142"/>
+      <c r="Z50" s="142"/>
+      <c r="AA50" s="142"/>
+      <c r="AB50" s="142"/>
+      <c r="AC50" s="142"/>
+      <c r="AD50" s="142"/>
+      <c r="AE50" s="142"/>
+      <c r="AF50" s="142"/>
+      <c r="AG50" s="142"/>
+      <c r="AH50" s="142"/>
+      <c r="AI50" s="142"/>
+      <c r="AJ50" s="142"/>
+      <c r="AK50" s="142"/>
+      <c r="AL50" s="142"/>
+      <c r="AM50" s="142"/>
+      <c r="AN50" s="142"/>
+      <c r="AO50" s="142"/>
+      <c r="AP50" s="142"/>
+      <c r="AQ50" s="142"/>
+      <c r="AR50" s="142"/>
+      <c r="AS50" s="142"/>
+      <c r="AT50" s="142"/>
+      <c r="AU50" s="142"/>
+      <c r="AV50" s="142"/>
+      <c r="AW50" s="142"/>
+      <c r="AX50" s="142"/>
+      <c r="AY50" s="142"/>
+      <c r="AZ50" s="142"/>
+      <c r="BA50" s="142"/>
+      <c r="BB50" s="142"/>
+      <c r="BC50" s="142"/>
+      <c r="BD50" s="142"/>
+      <c r="BE50" s="143"/>
     </row>
     <row r="51" spans="2:57" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B51" s="158"/>
-      <c r="C51" s="159"/>
-      <c r="D51" s="158"/>
-      <c r="E51" s="166"/>
-      <c r="F51" s="166"/>
-      <c r="G51" s="166"/>
-      <c r="H51" s="166"/>
-      <c r="I51" s="159"/>
-      <c r="J51" s="158"/>
-      <c r="K51" s="166"/>
-      <c r="L51" s="166"/>
-      <c r="M51" s="166"/>
-      <c r="N51" s="166"/>
-      <c r="O51" s="166"/>
-      <c r="P51" s="159"/>
-      <c r="Q51" s="158"/>
-      <c r="R51" s="166"/>
-      <c r="S51" s="166"/>
-      <c r="T51" s="159"/>
-      <c r="U51" s="158"/>
-      <c r="V51" s="166"/>
-      <c r="W51" s="159"/>
-      <c r="X51" s="158"/>
-      <c r="Y51" s="166"/>
-      <c r="Z51" s="166"/>
-      <c r="AA51" s="166"/>
-      <c r="AB51" s="166"/>
-      <c r="AC51" s="166"/>
-      <c r="AD51" s="166"/>
-      <c r="AE51" s="166"/>
-      <c r="AF51" s="166"/>
-      <c r="AG51" s="166"/>
-      <c r="AH51" s="166"/>
-      <c r="AI51" s="166"/>
-      <c r="AJ51" s="166"/>
-      <c r="AK51" s="166"/>
-      <c r="AL51" s="166"/>
-      <c r="AM51" s="166"/>
-      <c r="AN51" s="166"/>
-      <c r="AO51" s="166"/>
-      <c r="AP51" s="166"/>
-      <c r="AQ51" s="166"/>
-      <c r="AR51" s="166"/>
-      <c r="AS51" s="166"/>
-      <c r="AT51" s="166"/>
-      <c r="AU51" s="166"/>
-      <c r="AV51" s="166"/>
-      <c r="AW51" s="166"/>
-      <c r="AX51" s="166"/>
-      <c r="AY51" s="166"/>
-      <c r="AZ51" s="166"/>
-      <c r="BA51" s="166"/>
-      <c r="BB51" s="166"/>
-      <c r="BC51" s="166"/>
-      <c r="BD51" s="166"/>
-      <c r="BE51" s="159"/>
+      <c r="B51" s="144"/>
+      <c r="C51" s="146"/>
+      <c r="D51" s="144"/>
+      <c r="E51" s="145"/>
+      <c r="F51" s="145"/>
+      <c r="G51" s="145"/>
+      <c r="H51" s="145"/>
+      <c r="I51" s="146"/>
+      <c r="J51" s="144"/>
+      <c r="K51" s="145"/>
+      <c r="L51" s="145"/>
+      <c r="M51" s="145"/>
+      <c r="N51" s="145"/>
+      <c r="O51" s="145"/>
+      <c r="P51" s="146"/>
+      <c r="Q51" s="144"/>
+      <c r="R51" s="145"/>
+      <c r="S51" s="145"/>
+      <c r="T51" s="146"/>
+      <c r="U51" s="144"/>
+      <c r="V51" s="145"/>
+      <c r="W51" s="146"/>
+      <c r="X51" s="144"/>
+      <c r="Y51" s="145"/>
+      <c r="Z51" s="145"/>
+      <c r="AA51" s="145"/>
+      <c r="AB51" s="145"/>
+      <c r="AC51" s="145"/>
+      <c r="AD51" s="145"/>
+      <c r="AE51" s="145"/>
+      <c r="AF51" s="145"/>
+      <c r="AG51" s="145"/>
+      <c r="AH51" s="145"/>
+      <c r="AI51" s="145"/>
+      <c r="AJ51" s="145"/>
+      <c r="AK51" s="145"/>
+      <c r="AL51" s="145"/>
+      <c r="AM51" s="145"/>
+      <c r="AN51" s="145"/>
+      <c r="AO51" s="145"/>
+      <c r="AP51" s="145"/>
+      <c r="AQ51" s="145"/>
+      <c r="AR51" s="145"/>
+      <c r="AS51" s="145"/>
+      <c r="AT51" s="145"/>
+      <c r="AU51" s="145"/>
+      <c r="AV51" s="145"/>
+      <c r="AW51" s="145"/>
+      <c r="AX51" s="145"/>
+      <c r="AY51" s="145"/>
+      <c r="AZ51" s="145"/>
+      <c r="BA51" s="145"/>
+      <c r="BB51" s="145"/>
+      <c r="BC51" s="145"/>
+      <c r="BD51" s="145"/>
+      <c r="BE51" s="146"/>
     </row>
     <row r="52" spans="2:57" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B52" s="68" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C52" s="69"/>
       <c r="D52" s="69"/>
@@ -5253,12 +5283,12 @@
       <c r="BE52" s="70"/>
     </row>
     <row r="53" spans="2:57" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B53" s="169">
+      <c r="B53" s="137">
         <v>1</v>
       </c>
-      <c r="C53" s="170"/>
+      <c r="C53" s="138"/>
       <c r="D53" s="16" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E53" s="17"/>
       <c r="F53" s="17"/>
@@ -5266,7 +5296,7 @@
       <c r="H53" s="17"/>
       <c r="I53" s="18"/>
       <c r="J53" s="39" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K53" s="17"/>
       <c r="L53" s="17"/>
@@ -5322,7 +5352,7 @@
     </row>
     <row r="54" spans="2:57" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B54" s="68" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C54" s="69"/>
       <c r="D54" s="69"/>
@@ -5381,12 +5411,12 @@
       <c r="BE54" s="70"/>
     </row>
     <row r="55" spans="2:57" ht="13.8" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B55" s="169">
+      <c r="B55" s="137">
         <v>1</v>
       </c>
-      <c r="C55" s="170"/>
+      <c r="C55" s="138"/>
       <c r="D55" s="16" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E55" s="17"/>
       <c r="F55" s="17"/>
@@ -5394,7 +5424,7 @@
       <c r="H55" s="17"/>
       <c r="I55" s="18"/>
       <c r="J55" s="39" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K55" s="17"/>
       <c r="L55" s="17"/>
@@ -5450,7 +5480,7 @@
     </row>
     <row r="56" spans="2:57" ht="13.8" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B56" s="68" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C56" s="69"/>
       <c r="D56" s="69"/>
@@ -5509,12 +5539,12 @@
       <c r="BE56" s="70"/>
     </row>
     <row r="57" spans="2:57" ht="13.8" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B57" s="169">
+      <c r="B57" s="137">
         <v>1</v>
       </c>
-      <c r="C57" s="170"/>
+      <c r="C57" s="138"/>
       <c r="D57" s="16" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E57" s="17"/>
       <c r="F57" s="17"/>
@@ -5522,7 +5552,7 @@
       <c r="H57" s="17"/>
       <c r="I57" s="18"/>
       <c r="J57" s="39" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K57" s="17"/>
       <c r="L57" s="17"/>
@@ -5637,10 +5667,10 @@
       <c r="BE58" s="70"/>
     </row>
     <row r="59" spans="2:57" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B59" s="169">
+      <c r="B59" s="137">
         <v>1</v>
       </c>
-      <c r="C59" s="170"/>
+      <c r="C59" s="138"/>
       <c r="D59" s="16" t="s">
         <v>33</v>
       </c>
@@ -5759,10 +5789,10 @@
       <c r="BE60" s="70"/>
     </row>
     <row r="61" spans="2:57" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B61" s="169">
+      <c r="B61" s="137">
         <v>1</v>
       </c>
-      <c r="C61" s="170"/>
+      <c r="C61" s="138"/>
       <c r="D61" s="25" t="s">
         <v>59</v>
       </c>
@@ -5828,29 +5858,12 @@
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="U50:W51"/>
-    <mergeCell ref="X50:BE51"/>
-    <mergeCell ref="Q50:T51"/>
-    <mergeCell ref="J50:P51"/>
-    <mergeCell ref="B50:C51"/>
-    <mergeCell ref="D50:I51"/>
+    <mergeCell ref="B2:N3"/>
+    <mergeCell ref="J32:O32"/>
+    <mergeCell ref="B31:C32"/>
+    <mergeCell ref="D31:I32"/>
+    <mergeCell ref="W31:X31"/>
+    <mergeCell ref="V31:V32"/>
     <mergeCell ref="AK31:AL32"/>
     <mergeCell ref="AM31:AP32"/>
     <mergeCell ref="AD31:AE32"/>
@@ -5863,12 +5876,29 @@
     <mergeCell ref="AH31:AJ32"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B34:BE34"/>
-    <mergeCell ref="B2:N3"/>
-    <mergeCell ref="J32:O32"/>
-    <mergeCell ref="B31:C32"/>
-    <mergeCell ref="D31:I32"/>
-    <mergeCell ref="W31:X31"/>
-    <mergeCell ref="V31:V32"/>
+    <mergeCell ref="U50:W51"/>
+    <mergeCell ref="X50:BE51"/>
+    <mergeCell ref="Q50:T51"/>
+    <mergeCell ref="J50:P51"/>
+    <mergeCell ref="B50:C51"/>
+    <mergeCell ref="D50:I51"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B57:C57"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
@@ -5894,7 +5924,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61CFF209-E7A1-4B09-98D6-DBFC0DD483BC}">
-  <dimension ref="A1:AN39"/>
+  <dimension ref="A1:AN49"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3.33203125" style="26" customWidth="1"/>
@@ -5993,7 +6023,7 @@
       <c r="J6" s="45"/>
       <c r="K6" s="48"/>
       <c r="L6" s="85" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="M6" s="35"/>
       <c r="N6" s="35"/>
@@ -6046,7 +6076,7 @@
       <c r="B8" s="52"/>
       <c r="C8" s="35"/>
       <c r="D8" s="53" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E8" s="35"/>
       <c r="F8" s="35"/>
@@ -6063,7 +6093,7 @@
       <c r="P8" s="28"/>
       <c r="Q8" s="29"/>
       <c r="R8" s="30" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="S8" s="31"/>
       <c r="T8" s="31"/>
@@ -6103,7 +6133,7 @@
       <c r="P9" s="86"/>
       <c r="Q9" s="86"/>
       <c r="R9" s="33" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="S9" s="33"/>
       <c r="T9" s="33"/>
@@ -6169,7 +6199,7 @@
       <c r="J11" s="35"/>
       <c r="K11" s="55"/>
       <c r="L11" s="53" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="M11" s="35"/>
       <c r="N11" s="35"/>
@@ -6253,7 +6283,7 @@
       <c r="P13" s="28"/>
       <c r="Q13" s="29"/>
       <c r="R13" s="30" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="S13" s="31"/>
       <c r="T13" s="31"/>
@@ -6290,14 +6320,14 @@
       <c r="K14" s="55"/>
       <c r="L14" s="35"/>
       <c r="M14" s="172" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N14" s="173"/>
       <c r="O14" s="173"/>
       <c r="P14" s="173"/>
       <c r="Q14" s="174"/>
       <c r="R14" s="33" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="S14" s="33"/>
       <c r="T14" s="33"/>
@@ -6373,7 +6403,7 @@
       <c r="J16" s="35"/>
       <c r="K16" s="55"/>
       <c r="L16" s="35" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="M16" s="35"/>
       <c r="N16" s="35"/>
@@ -6449,7 +6479,7 @@
       </c>
       <c r="C18" s="35"/>
       <c r="D18" s="53" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E18" s="35"/>
       <c r="F18" s="35"/>
@@ -6535,7 +6565,7 @@
       <c r="B20" s="52"/>
       <c r="C20" s="35"/>
       <c r="D20" s="53" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E20" s="35"/>
       <c r="F20" s="35"/>
@@ -6574,56 +6604,50 @@
       <c r="AM20" s="55"/>
     </row>
     <row r="21" spans="2:39" s="26" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="44">
-        <v>3</v>
-      </c>
-      <c r="C21" s="45"/>
-      <c r="D21" s="46" t="s">
-        <v>94</v>
-      </c>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="47"/>
-      <c r="J21" s="45"/>
-      <c r="K21" s="48"/>
-      <c r="L21" s="45" t="s">
-        <v>89</v>
-      </c>
-      <c r="M21" s="45"/>
-      <c r="N21" s="45"/>
-      <c r="O21" s="45"/>
-      <c r="P21" s="45"/>
-      <c r="Q21" s="45"/>
-      <c r="R21" s="45"/>
-      <c r="S21" s="45"/>
-      <c r="T21" s="45"/>
-      <c r="U21" s="45"/>
-      <c r="V21" s="45"/>
-      <c r="W21" s="45"/>
-      <c r="X21" s="45"/>
-      <c r="Y21" s="45"/>
-      <c r="Z21" s="45"/>
-      <c r="AA21" s="45"/>
-      <c r="AB21" s="45"/>
-      <c r="AC21" s="45"/>
-      <c r="AD21" s="45"/>
-      <c r="AE21" s="45"/>
-      <c r="AF21" s="45"/>
-      <c r="AG21" s="46"/>
-      <c r="AH21" s="45"/>
-      <c r="AI21" s="45"/>
-      <c r="AJ21" s="45"/>
-      <c r="AK21" s="45"/>
-      <c r="AL21" s="45"/>
-      <c r="AM21" s="48"/>
+      <c r="B21" s="52"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="54"/>
+      <c r="J21" s="35"/>
+      <c r="K21" s="55"/>
+      <c r="L21" s="35"/>
+      <c r="M21" s="35"/>
+      <c r="N21" s="35"/>
+      <c r="O21" s="35"/>
+      <c r="P21" s="35"/>
+      <c r="Q21" s="35"/>
+      <c r="R21" s="35"/>
+      <c r="S21" s="35"/>
+      <c r="T21" s="35"/>
+      <c r="U21" s="35"/>
+      <c r="V21" s="35"/>
+      <c r="W21" s="35"/>
+      <c r="X21" s="35"/>
+      <c r="Y21" s="35"/>
+      <c r="Z21" s="35"/>
+      <c r="AA21" s="35"/>
+      <c r="AB21" s="35"/>
+      <c r="AC21" s="35"/>
+      <c r="AD21" s="35"/>
+      <c r="AE21" s="35"/>
+      <c r="AF21" s="35"/>
+      <c r="AG21" s="53"/>
+      <c r="AH21" s="35"/>
+      <c r="AI21" s="35"/>
+      <c r="AJ21" s="35"/>
+      <c r="AK21" s="35"/>
+      <c r="AL21" s="35"/>
+      <c r="AM21" s="55"/>
     </row>
     <row r="22" spans="2:39" s="26" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="52"/>
       <c r="C22" s="35"/>
-      <c r="D22" s="73" t="s">
-        <v>95</v>
+      <c r="D22" s="53" t="s">
+        <v>97</v>
       </c>
       <c r="E22" s="35"/>
       <c r="F22" s="35"/>
@@ -6665,7 +6689,7 @@
       <c r="B23" s="52"/>
       <c r="C23" s="35"/>
       <c r="D23" s="53" t="s">
-        <v>34</v>
+        <v>118</v>
       </c>
       <c r="E23" s="35"/>
       <c r="F23" s="35"/>
@@ -6675,27 +6699,23 @@
       <c r="J23" s="35"/>
       <c r="K23" s="55"/>
       <c r="L23" s="35"/>
-      <c r="M23" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="N23" s="28"/>
-      <c r="O23" s="28"/>
-      <c r="P23" s="28"/>
-      <c r="Q23" s="29"/>
-      <c r="R23" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="S23" s="31"/>
-      <c r="T23" s="31"/>
-      <c r="U23" s="31"/>
-      <c r="V23" s="31"/>
-      <c r="W23" s="31"/>
-      <c r="X23" s="31"/>
-      <c r="Y23" s="31"/>
-      <c r="Z23" s="31"/>
-      <c r="AA23" s="31"/>
-      <c r="AB23" s="31"/>
-      <c r="AC23" s="32"/>
+      <c r="M23" s="35"/>
+      <c r="N23" s="35"/>
+      <c r="O23" s="35"/>
+      <c r="P23" s="35"/>
+      <c r="Q23" s="35"/>
+      <c r="R23" s="35"/>
+      <c r="S23" s="35"/>
+      <c r="T23" s="35"/>
+      <c r="U23" s="35"/>
+      <c r="V23" s="35"/>
+      <c r="W23" s="35"/>
+      <c r="X23" s="35"/>
+      <c r="Y23" s="35"/>
+      <c r="Z23" s="35"/>
+      <c r="AA23" s="35"/>
+      <c r="AB23" s="35"/>
+      <c r="AC23" s="35"/>
       <c r="AD23" s="35"/>
       <c r="AE23" s="35"/>
       <c r="AF23" s="35"/>
@@ -6710,9 +6730,7 @@
     <row r="24" spans="2:39" s="26" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="52"/>
       <c r="C24" s="35"/>
-      <c r="D24" s="53" t="s">
-        <v>102</v>
-      </c>
+      <c r="D24" s="53"/>
       <c r="E24" s="35"/>
       <c r="F24" s="35"/>
       <c r="G24" s="35"/>
@@ -6721,27 +6739,23 @@
       <c r="J24" s="35"/>
       <c r="K24" s="55"/>
       <c r="L24" s="35"/>
-      <c r="M24" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="N24" s="28"/>
-      <c r="O24" s="28"/>
-      <c r="P24" s="28"/>
-      <c r="Q24" s="29"/>
-      <c r="R24" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="S24" s="33"/>
-      <c r="T24" s="33"/>
-      <c r="U24" s="33"/>
-      <c r="V24" s="33"/>
-      <c r="W24" s="33"/>
-      <c r="X24" s="33"/>
-      <c r="Y24" s="33"/>
-      <c r="Z24" s="33"/>
-      <c r="AA24" s="33"/>
-      <c r="AB24" s="33"/>
-      <c r="AC24" s="34"/>
+      <c r="M24" s="35"/>
+      <c r="N24" s="35"/>
+      <c r="O24" s="35"/>
+      <c r="P24" s="35"/>
+      <c r="Q24" s="35"/>
+      <c r="R24" s="35"/>
+      <c r="S24" s="35"/>
+      <c r="T24" s="35"/>
+      <c r="U24" s="35"/>
+      <c r="V24" s="35"/>
+      <c r="W24" s="35"/>
+      <c r="X24" s="35"/>
+      <c r="Y24" s="35"/>
+      <c r="Z24" s="35"/>
+      <c r="AA24" s="35"/>
+      <c r="AB24" s="35"/>
+      <c r="AC24" s="35"/>
       <c r="AD24" s="35"/>
       <c r="AE24" s="35"/>
       <c r="AF24" s="35"/>
@@ -6754,44 +6768,56 @@
       <c r="AM24" s="55"/>
     </row>
     <row r="25" spans="2:39" s="26" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="52"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="53"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="35"/>
-      <c r="I25" s="54"/>
-      <c r="J25" s="35"/>
-      <c r="K25" s="55"/>
-      <c r="L25" s="35"/>
-      <c r="S25" s="35"/>
-      <c r="T25" s="35"/>
-      <c r="U25" s="35"/>
-      <c r="V25" s="35"/>
-      <c r="W25" s="35"/>
-      <c r="X25" s="35"/>
-      <c r="Y25" s="35"/>
-      <c r="Z25" s="35"/>
-      <c r="AA25" s="35"/>
-      <c r="AB25" s="35"/>
-      <c r="AC25" s="35"/>
-      <c r="AD25" s="35"/>
-      <c r="AE25" s="35"/>
-      <c r="AF25" s="35"/>
-      <c r="AG25" s="53"/>
-      <c r="AH25" s="35"/>
-      <c r="AI25" s="35"/>
-      <c r="AJ25" s="35"/>
-      <c r="AK25" s="35"/>
-      <c r="AL25" s="35"/>
-      <c r="AM25" s="55"/>
+      <c r="B25" s="44">
+        <v>3</v>
+      </c>
+      <c r="C25" s="45"/>
+      <c r="D25" s="46" t="s">
+        <v>113</v>
+      </c>
+      <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="45"/>
+      <c r="H25" s="45"/>
+      <c r="I25" s="47"/>
+      <c r="J25" s="45"/>
+      <c r="K25" s="48"/>
+      <c r="L25" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="M25" s="45"/>
+      <c r="N25" s="45"/>
+      <c r="O25" s="45"/>
+      <c r="P25" s="45"/>
+      <c r="Q25" s="45"/>
+      <c r="R25" s="45"/>
+      <c r="S25" s="45"/>
+      <c r="T25" s="45"/>
+      <c r="U25" s="45"/>
+      <c r="V25" s="45"/>
+      <c r="W25" s="45"/>
+      <c r="X25" s="45"/>
+      <c r="Y25" s="45"/>
+      <c r="Z25" s="45"/>
+      <c r="AA25" s="45"/>
+      <c r="AB25" s="45"/>
+      <c r="AC25" s="45"/>
+      <c r="AD25" s="45"/>
+      <c r="AE25" s="45"/>
+      <c r="AF25" s="45"/>
+      <c r="AG25" s="46"/>
+      <c r="AH25" s="45"/>
+      <c r="AI25" s="45"/>
+      <c r="AJ25" s="45"/>
+      <c r="AK25" s="45"/>
+      <c r="AL25" s="45"/>
+      <c r="AM25" s="48"/>
     </row>
     <row r="26" spans="2:39" s="26" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="52"/>
       <c r="C26" s="35"/>
       <c r="D26" s="53" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="E26" s="35"/>
       <c r="F26" s="35"/>
@@ -6800,9 +6826,24 @@
       <c r="I26" s="54"/>
       <c r="J26" s="35"/>
       <c r="K26" s="55"/>
-      <c r="L26" s="35" t="s">
-        <v>92</v>
-      </c>
+      <c r="L26" s="35"/>
+      <c r="M26" s="35"/>
+      <c r="N26" s="35"/>
+      <c r="O26" s="35"/>
+      <c r="P26" s="35"/>
+      <c r="Q26" s="35"/>
+      <c r="R26" s="35"/>
+      <c r="S26" s="35"/>
+      <c r="T26" s="35"/>
+      <c r="U26" s="35"/>
+      <c r="V26" s="35"/>
+      <c r="W26" s="35"/>
+      <c r="X26" s="35"/>
+      <c r="Y26" s="35"/>
+      <c r="Z26" s="35"/>
+      <c r="AA26" s="35"/>
+      <c r="AB26" s="35"/>
+      <c r="AC26" s="35"/>
       <c r="AD26" s="35"/>
       <c r="AE26" s="35"/>
       <c r="AF26" s="35"/>
@@ -6818,7 +6859,7 @@
       <c r="B27" s="52"/>
       <c r="C27" s="35"/>
       <c r="D27" s="53" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E27" s="35"/>
       <c r="F27" s="35"/>
@@ -6827,23 +6868,28 @@
       <c r="I27" s="54"/>
       <c r="J27" s="35"/>
       <c r="K27" s="55"/>
-      <c r="M27" s="35"/>
-      <c r="N27" s="35"/>
-      <c r="O27" s="35"/>
-      <c r="P27" s="35"/>
-      <c r="Q27" s="35"/>
-      <c r="R27" s="35"/>
-      <c r="S27" s="35"/>
-      <c r="T27" s="35"/>
-      <c r="U27" s="35"/>
-      <c r="V27" s="35"/>
-      <c r="W27" s="35"/>
-      <c r="X27" s="35"/>
-      <c r="Y27" s="35"/>
-      <c r="Z27" s="35"/>
-      <c r="AA27" s="35"/>
-      <c r="AB27" s="35"/>
-      <c r="AC27" s="35"/>
+      <c r="L27" s="35"/>
+      <c r="M27" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="N27" s="28"/>
+      <c r="O27" s="28"/>
+      <c r="P27" s="28"/>
+      <c r="Q27" s="29"/>
+      <c r="R27" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="S27" s="31"/>
+      <c r="T27" s="31"/>
+      <c r="U27" s="31"/>
+      <c r="V27" s="31"/>
+      <c r="W27" s="31"/>
+      <c r="X27" s="31"/>
+      <c r="Y27" s="31"/>
+      <c r="Z27" s="31"/>
+      <c r="AA27" s="31"/>
+      <c r="AB27" s="31"/>
+      <c r="AC27" s="32"/>
       <c r="AD27" s="35"/>
       <c r="AE27" s="35"/>
       <c r="AF27" s="35"/>
@@ -6858,32 +6904,36 @@
     <row r="28" spans="2:39" s="26" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="52"/>
       <c r="C28" s="35"/>
-      <c r="D28" s="58"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
-      <c r="I28" s="72"/>
-      <c r="J28" s="33"/>
-      <c r="K28" s="34"/>
+      <c r="D28" s="53"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="35"/>
+      <c r="I28" s="54"/>
+      <c r="J28" s="35"/>
+      <c r="K28" s="55"/>
       <c r="L28" s="35"/>
-      <c r="M28" s="35"/>
-      <c r="N28" s="35"/>
-      <c r="O28" s="35"/>
-      <c r="P28" s="35"/>
-      <c r="Q28" s="35"/>
-      <c r="R28" s="35"/>
-      <c r="S28" s="35"/>
-      <c r="T28" s="35"/>
-      <c r="U28" s="35"/>
-      <c r="V28" s="35"/>
-      <c r="W28" s="35"/>
-      <c r="X28" s="35"/>
-      <c r="Y28" s="35"/>
-      <c r="Z28" s="35"/>
-      <c r="AA28" s="35"/>
-      <c r="AB28" s="35"/>
-      <c r="AC28" s="35"/>
+      <c r="M28" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="N28" s="28"/>
+      <c r="O28" s="28"/>
+      <c r="P28" s="28"/>
+      <c r="Q28" s="29"/>
+      <c r="R28" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="S28" s="33"/>
+      <c r="T28" s="33"/>
+      <c r="U28" s="33"/>
+      <c r="V28" s="33"/>
+      <c r="W28" s="33"/>
+      <c r="X28" s="33"/>
+      <c r="Y28" s="33"/>
+      <c r="Z28" s="33"/>
+      <c r="AA28" s="33"/>
+      <c r="AB28" s="33"/>
+      <c r="AC28" s="34"/>
       <c r="AD28" s="35"/>
       <c r="AE28" s="35"/>
       <c r="AF28" s="35"/>
@@ -6895,269 +6945,653 @@
       <c r="AL28" s="35"/>
       <c r="AM28" s="55"/>
     </row>
-    <row r="29" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="60">
+    <row r="29" spans="2:39" s="26" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="52"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="53" t="s">
+        <v>97</v>
+      </c>
+      <c r="E29" s="35"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="35"/>
+      <c r="I29" s="54"/>
+      <c r="J29" s="35"/>
+      <c r="K29" s="55"/>
+      <c r="L29" s="35"/>
+      <c r="S29" s="35"/>
+      <c r="T29" s="35"/>
+      <c r="U29" s="35"/>
+      <c r="V29" s="35"/>
+      <c r="W29" s="35"/>
+      <c r="X29" s="35"/>
+      <c r="Y29" s="35"/>
+      <c r="Z29" s="35"/>
+      <c r="AA29" s="35"/>
+      <c r="AB29" s="35"/>
+      <c r="AC29" s="35"/>
+      <c r="AD29" s="35"/>
+      <c r="AE29" s="35"/>
+      <c r="AF29" s="35"/>
+      <c r="AG29" s="53"/>
+      <c r="AH29" s="35"/>
+      <c r="AI29" s="35"/>
+      <c r="AJ29" s="35"/>
+      <c r="AK29" s="35"/>
+      <c r="AL29" s="35"/>
+      <c r="AM29" s="55"/>
+    </row>
+    <row r="30" spans="2:39" s="26" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="52"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="53" t="s">
+        <v>117</v>
+      </c>
+      <c r="E30" s="35"/>
+      <c r="F30" s="35"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="35"/>
+      <c r="I30" s="54"/>
+      <c r="J30" s="35"/>
+      <c r="K30" s="55"/>
+      <c r="L30" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="AD30" s="35"/>
+      <c r="AE30" s="35"/>
+      <c r="AF30" s="35"/>
+      <c r="AG30" s="53"/>
+      <c r="AH30" s="35"/>
+      <c r="AI30" s="35"/>
+      <c r="AJ30" s="35"/>
+      <c r="AK30" s="35"/>
+      <c r="AL30" s="35"/>
+      <c r="AM30" s="55"/>
+    </row>
+    <row r="31" spans="2:39" s="26" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="52"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="58"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="72"/>
+      <c r="J31" s="33"/>
+      <c r="K31" s="34"/>
+      <c r="L31" s="35"/>
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
+      <c r="O31" s="35"/>
+      <c r="P31" s="35"/>
+      <c r="Q31" s="35"/>
+      <c r="R31" s="35"/>
+      <c r="S31" s="35"/>
+      <c r="T31" s="35"/>
+      <c r="U31" s="35"/>
+      <c r="V31" s="35"/>
+      <c r="W31" s="35"/>
+      <c r="X31" s="35"/>
+      <c r="Y31" s="35"/>
+      <c r="Z31" s="35"/>
+      <c r="AA31" s="35"/>
+      <c r="AB31" s="35"/>
+      <c r="AC31" s="35"/>
+      <c r="AD31" s="35"/>
+      <c r="AE31" s="35"/>
+      <c r="AF31" s="35"/>
+      <c r="AG31" s="53"/>
+      <c r="AH31" s="35"/>
+      <c r="AI31" s="35"/>
+      <c r="AJ31" s="35"/>
+      <c r="AK31" s="35"/>
+      <c r="AL31" s="35"/>
+      <c r="AM31" s="55"/>
+    </row>
+    <row r="32" spans="2:39" s="26" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="44">
         <v>4</v>
       </c>
-      <c r="C29" s="61"/>
-      <c r="D29" s="74" t="s">
+      <c r="C32" s="45"/>
+      <c r="D32" s="46" t="s">
+        <v>114</v>
+      </c>
+      <c r="E32" s="45"/>
+      <c r="F32" s="45"/>
+      <c r="G32" s="45"/>
+      <c r="H32" s="45"/>
+      <c r="I32" s="47"/>
+      <c r="J32" s="45"/>
+      <c r="K32" s="48"/>
+      <c r="L32" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="M32" s="45"/>
+      <c r="N32" s="45"/>
+      <c r="O32" s="45"/>
+      <c r="P32" s="45"/>
+      <c r="Q32" s="45"/>
+      <c r="R32" s="45"/>
+      <c r="S32" s="45"/>
+      <c r="T32" s="45"/>
+      <c r="U32" s="45"/>
+      <c r="V32" s="45"/>
+      <c r="W32" s="45"/>
+      <c r="X32" s="45"/>
+      <c r="Y32" s="45"/>
+      <c r="Z32" s="45"/>
+      <c r="AA32" s="45"/>
+      <c r="AB32" s="45"/>
+      <c r="AC32" s="45"/>
+      <c r="AD32" s="45"/>
+      <c r="AE32" s="45"/>
+      <c r="AF32" s="45"/>
+      <c r="AG32" s="46"/>
+      <c r="AH32" s="45"/>
+      <c r="AI32" s="45"/>
+      <c r="AJ32" s="45"/>
+      <c r="AK32" s="45"/>
+      <c r="AL32" s="45"/>
+      <c r="AM32" s="48"/>
+    </row>
+    <row r="33" spans="2:39" s="26" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="52"/>
+      <c r="C33" s="35"/>
+      <c r="D33" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="E33" s="35"/>
+      <c r="F33" s="35"/>
+      <c r="G33" s="35"/>
+      <c r="H33" s="35"/>
+      <c r="I33" s="54"/>
+      <c r="J33" s="35"/>
+      <c r="K33" s="55"/>
+      <c r="L33" s="35"/>
+      <c r="M33" s="35"/>
+      <c r="N33" s="35"/>
+      <c r="O33" s="35"/>
+      <c r="P33" s="35"/>
+      <c r="Q33" s="35"/>
+      <c r="R33" s="35"/>
+      <c r="S33" s="35"/>
+      <c r="T33" s="35"/>
+      <c r="U33" s="35"/>
+      <c r="V33" s="35"/>
+      <c r="W33" s="35"/>
+      <c r="X33" s="35"/>
+      <c r="Y33" s="35"/>
+      <c r="Z33" s="35"/>
+      <c r="AA33" s="35"/>
+      <c r="AB33" s="35"/>
+      <c r="AC33" s="35"/>
+      <c r="AD33" s="35"/>
+      <c r="AE33" s="35"/>
+      <c r="AF33" s="35"/>
+      <c r="AG33" s="53"/>
+      <c r="AH33" s="35"/>
+      <c r="AI33" s="35"/>
+      <c r="AJ33" s="35"/>
+      <c r="AK33" s="35"/>
+      <c r="AL33" s="35"/>
+      <c r="AM33" s="55"/>
+    </row>
+    <row r="34" spans="2:39" s="26" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="52"/>
+      <c r="C34" s="35"/>
+      <c r="D34" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="E34" s="35"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="35"/>
+      <c r="I34" s="54"/>
+      <c r="J34" s="35"/>
+      <c r="K34" s="55"/>
+      <c r="L34" s="35"/>
+      <c r="M34" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="N34" s="28"/>
+      <c r="O34" s="28"/>
+      <c r="P34" s="28"/>
+      <c r="Q34" s="29"/>
+      <c r="R34" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="S34" s="31"/>
+      <c r="T34" s="31"/>
+      <c r="U34" s="31"/>
+      <c r="V34" s="31"/>
+      <c r="W34" s="31"/>
+      <c r="X34" s="31"/>
+      <c r="Y34" s="31"/>
+      <c r="Z34" s="31"/>
+      <c r="AA34" s="31"/>
+      <c r="AB34" s="31"/>
+      <c r="AC34" s="32"/>
+      <c r="AD34" s="35"/>
+      <c r="AE34" s="35"/>
+      <c r="AF34" s="35"/>
+      <c r="AG34" s="53"/>
+      <c r="AH34" s="35"/>
+      <c r="AI34" s="35"/>
+      <c r="AJ34" s="35"/>
+      <c r="AK34" s="35"/>
+      <c r="AL34" s="35"/>
+      <c r="AM34" s="55"/>
+    </row>
+    <row r="35" spans="2:39" s="26" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="52"/>
+      <c r="C35" s="35"/>
+      <c r="D35" s="53"/>
+      <c r="E35" s="35"/>
+      <c r="F35" s="35"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="35"/>
+      <c r="I35" s="54"/>
+      <c r="J35" s="35"/>
+      <c r="K35" s="55"/>
+      <c r="L35" s="35"/>
+      <c r="M35" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="N35" s="28"/>
+      <c r="O35" s="28"/>
+      <c r="P35" s="28"/>
+      <c r="Q35" s="29"/>
+      <c r="R35" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="S35" s="33"/>
+      <c r="T35" s="33"/>
+      <c r="U35" s="33"/>
+      <c r="V35" s="33"/>
+      <c r="W35" s="33"/>
+      <c r="X35" s="33"/>
+      <c r="Y35" s="33"/>
+      <c r="Z35" s="33"/>
+      <c r="AA35" s="33"/>
+      <c r="AB35" s="33"/>
+      <c r="AC35" s="34"/>
+      <c r="AD35" s="35"/>
+      <c r="AE35" s="35"/>
+      <c r="AF35" s="35"/>
+      <c r="AG35" s="53"/>
+      <c r="AH35" s="35"/>
+      <c r="AI35" s="35"/>
+      <c r="AJ35" s="35"/>
+      <c r="AK35" s="35"/>
+      <c r="AL35" s="35"/>
+      <c r="AM35" s="55"/>
+    </row>
+    <row r="36" spans="2:39" s="26" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="52"/>
+      <c r="C36" s="35"/>
+      <c r="D36" s="53" t="s">
+        <v>97</v>
+      </c>
+      <c r="E36" s="35"/>
+      <c r="F36" s="35"/>
+      <c r="G36" s="35"/>
+      <c r="H36" s="35"/>
+      <c r="I36" s="54"/>
+      <c r="J36" s="35"/>
+      <c r="K36" s="55"/>
+      <c r="L36" s="35"/>
+      <c r="S36" s="35"/>
+      <c r="T36" s="35"/>
+      <c r="U36" s="35"/>
+      <c r="V36" s="35"/>
+      <c r="W36" s="35"/>
+      <c r="X36" s="35"/>
+      <c r="Y36" s="35"/>
+      <c r="Z36" s="35"/>
+      <c r="AA36" s="35"/>
+      <c r="AB36" s="35"/>
+      <c r="AC36" s="35"/>
+      <c r="AD36" s="35"/>
+      <c r="AE36" s="35"/>
+      <c r="AF36" s="35"/>
+      <c r="AG36" s="53"/>
+      <c r="AH36" s="35"/>
+      <c r="AI36" s="35"/>
+      <c r="AJ36" s="35"/>
+      <c r="AK36" s="35"/>
+      <c r="AL36" s="35"/>
+      <c r="AM36" s="55"/>
+    </row>
+    <row r="37" spans="2:39" s="26" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="52"/>
+      <c r="C37" s="35"/>
+      <c r="D37" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="E37" s="35"/>
+      <c r="F37" s="35"/>
+      <c r="G37" s="35"/>
+      <c r="H37" s="35"/>
+      <c r="I37" s="54"/>
+      <c r="J37" s="35"/>
+      <c r="K37" s="55"/>
+      <c r="L37" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="AD37" s="35"/>
+      <c r="AE37" s="35"/>
+      <c r="AF37" s="35"/>
+      <c r="AG37" s="53"/>
+      <c r="AH37" s="35"/>
+      <c r="AI37" s="35"/>
+      <c r="AJ37" s="35"/>
+      <c r="AK37" s="35"/>
+      <c r="AL37" s="35"/>
+      <c r="AM37" s="55"/>
+    </row>
+    <row r="38" spans="2:39" s="26" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="52"/>
+      <c r="C38" s="35"/>
+      <c r="D38" s="58"/>
+      <c r="E38" s="33"/>
+      <c r="F38" s="33"/>
+      <c r="G38" s="33"/>
+      <c r="H38" s="33"/>
+      <c r="I38" s="72"/>
+      <c r="J38" s="33"/>
+      <c r="K38" s="34"/>
+      <c r="L38" s="35"/>
+      <c r="M38" s="35"/>
+      <c r="N38" s="35"/>
+      <c r="O38" s="35"/>
+      <c r="P38" s="35"/>
+      <c r="Q38" s="35"/>
+      <c r="R38" s="35"/>
+      <c r="S38" s="35"/>
+      <c r="T38" s="35"/>
+      <c r="U38" s="35"/>
+      <c r="V38" s="35"/>
+      <c r="W38" s="35"/>
+      <c r="X38" s="35"/>
+      <c r="Y38" s="35"/>
+      <c r="Z38" s="35"/>
+      <c r="AA38" s="35"/>
+      <c r="AB38" s="35"/>
+      <c r="AC38" s="35"/>
+      <c r="AD38" s="35"/>
+      <c r="AE38" s="35"/>
+      <c r="AF38" s="35"/>
+      <c r="AG38" s="53"/>
+      <c r="AH38" s="35"/>
+      <c r="AI38" s="35"/>
+      <c r="AJ38" s="35"/>
+      <c r="AK38" s="35"/>
+      <c r="AL38" s="35"/>
+      <c r="AM38" s="55"/>
+    </row>
+    <row r="39" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B39" s="60">
+        <v>5</v>
+      </c>
+      <c r="C39" s="61"/>
+      <c r="D39" s="74" t="s">
         <v>51</v>
       </c>
-      <c r="E29" s="75"/>
-      <c r="F29" s="75"/>
-      <c r="G29" s="75"/>
-      <c r="H29" s="75"/>
-      <c r="I29" s="75"/>
-      <c r="J29" s="75"/>
-      <c r="K29" s="76"/>
-      <c r="L29" s="75" t="s">
-        <v>88</v>
-      </c>
-      <c r="M29" s="75"/>
-      <c r="N29" s="75"/>
-      <c r="O29" s="75"/>
-      <c r="P29" s="75"/>
-      <c r="Q29" s="75"/>
-      <c r="R29" s="75"/>
-      <c r="S29" s="75"/>
-      <c r="T29" s="75"/>
-      <c r="U29" s="75"/>
-      <c r="V29" s="75"/>
-      <c r="W29" s="75"/>
-      <c r="X29" s="75"/>
-      <c r="Y29" s="75"/>
-      <c r="Z29" s="75"/>
-      <c r="AA29" s="75"/>
-      <c r="AB29" s="75"/>
-      <c r="AC29" s="75"/>
-      <c r="AD29" s="75"/>
-      <c r="AE29" s="75"/>
-      <c r="AF29" s="75"/>
-      <c r="AG29" s="74"/>
-      <c r="AH29" s="75"/>
-      <c r="AI29" s="75"/>
-      <c r="AJ29" s="75"/>
-      <c r="AK29" s="75"/>
-      <c r="AL29" s="75"/>
-      <c r="AM29" s="76"/>
-    </row>
-    <row r="30" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="57"/>
-      <c r="C30" s="38"/>
-      <c r="D30" s="77"/>
-      <c r="E30" s="78"/>
-      <c r="F30" s="78"/>
-      <c r="G30" s="78"/>
-      <c r="H30" s="78"/>
-      <c r="I30" s="78"/>
-      <c r="J30" s="78"/>
-      <c r="K30" s="79"/>
-      <c r="L30" s="78"/>
-      <c r="M30" s="78"/>
-      <c r="N30" s="78"/>
-      <c r="O30" s="78"/>
-      <c r="P30" s="78"/>
-      <c r="Q30" s="78"/>
-      <c r="R30" s="78"/>
-      <c r="S30" s="78"/>
-      <c r="T30" s="78"/>
-      <c r="U30" s="78"/>
-      <c r="V30" s="78"/>
-      <c r="W30" s="78"/>
-      <c r="X30" s="78"/>
-      <c r="Y30" s="78"/>
-      <c r="Z30" s="78"/>
-      <c r="AA30" s="78"/>
-      <c r="AB30" s="78"/>
-      <c r="AC30" s="78"/>
-      <c r="AD30" s="78"/>
-      <c r="AE30" s="78"/>
-      <c r="AF30" s="78"/>
-      <c r="AG30" s="77"/>
-      <c r="AH30" s="78"/>
-      <c r="AI30" s="78"/>
-      <c r="AJ30" s="78"/>
-      <c r="AK30" s="78"/>
-      <c r="AL30" s="78"/>
-      <c r="AM30" s="79"/>
-    </row>
-    <row r="31" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B31" s="60">
-        <v>5</v>
-      </c>
-      <c r="C31" s="61"/>
-      <c r="D31" s="74" t="s">
+      <c r="E39" s="75"/>
+      <c r="F39" s="75"/>
+      <c r="G39" s="75"/>
+      <c r="H39" s="75"/>
+      <c r="I39" s="75"/>
+      <c r="J39" s="75"/>
+      <c r="K39" s="76"/>
+      <c r="L39" s="75" t="s">
+        <v>87</v>
+      </c>
+      <c r="M39" s="75"/>
+      <c r="N39" s="75"/>
+      <c r="O39" s="75"/>
+      <c r="P39" s="75"/>
+      <c r="Q39" s="75"/>
+      <c r="R39" s="75"/>
+      <c r="S39" s="75"/>
+      <c r="T39" s="75"/>
+      <c r="U39" s="75"/>
+      <c r="V39" s="75"/>
+      <c r="W39" s="75"/>
+      <c r="X39" s="75"/>
+      <c r="Y39" s="75"/>
+      <c r="Z39" s="75"/>
+      <c r="AA39" s="75"/>
+      <c r="AB39" s="75"/>
+      <c r="AC39" s="75"/>
+      <c r="AD39" s="75"/>
+      <c r="AE39" s="75"/>
+      <c r="AF39" s="75"/>
+      <c r="AG39" s="74"/>
+      <c r="AH39" s="75"/>
+      <c r="AI39" s="75"/>
+      <c r="AJ39" s="75"/>
+      <c r="AK39" s="75"/>
+      <c r="AL39" s="75"/>
+      <c r="AM39" s="76"/>
+    </row>
+    <row r="40" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B40" s="57"/>
+      <c r="C40" s="38"/>
+      <c r="D40" s="77"/>
+      <c r="E40" s="78"/>
+      <c r="F40" s="78"/>
+      <c r="G40" s="78"/>
+      <c r="H40" s="78"/>
+      <c r="I40" s="78"/>
+      <c r="J40" s="78"/>
+      <c r="K40" s="79"/>
+      <c r="L40" s="78"/>
+      <c r="M40" s="78"/>
+      <c r="N40" s="78"/>
+      <c r="O40" s="78"/>
+      <c r="P40" s="78"/>
+      <c r="Q40" s="78"/>
+      <c r="R40" s="78"/>
+      <c r="S40" s="78"/>
+      <c r="T40" s="78"/>
+      <c r="U40" s="78"/>
+      <c r="V40" s="78"/>
+      <c r="W40" s="78"/>
+      <c r="X40" s="78"/>
+      <c r="Y40" s="78"/>
+      <c r="Z40" s="78"/>
+      <c r="AA40" s="78"/>
+      <c r="AB40" s="78"/>
+      <c r="AC40" s="78"/>
+      <c r="AD40" s="78"/>
+      <c r="AE40" s="78"/>
+      <c r="AF40" s="78"/>
+      <c r="AG40" s="77"/>
+      <c r="AH40" s="78"/>
+      <c r="AI40" s="78"/>
+      <c r="AJ40" s="78"/>
+      <c r="AK40" s="78"/>
+      <c r="AL40" s="78"/>
+      <c r="AM40" s="79"/>
+    </row>
+    <row r="41" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B41" s="60">
+        <v>6</v>
+      </c>
+      <c r="C41" s="61"/>
+      <c r="D41" s="74" t="s">
         <v>52</v>
       </c>
-      <c r="E31" s="75"/>
-      <c r="F31" s="75"/>
-      <c r="G31" s="75"/>
-      <c r="H31" s="75"/>
-      <c r="I31" s="75"/>
-      <c r="J31" s="75"/>
-      <c r="K31" s="76"/>
-      <c r="L31" s="75" t="s">
+      <c r="E41" s="75"/>
+      <c r="F41" s="75"/>
+      <c r="G41" s="75"/>
+      <c r="H41" s="75"/>
+      <c r="I41" s="75"/>
+      <c r="J41" s="75"/>
+      <c r="K41" s="76"/>
+      <c r="L41" s="75" t="s">
         <v>65</v>
       </c>
-      <c r="M31" s="75"/>
-      <c r="N31" s="75"/>
-      <c r="O31" s="75"/>
-      <c r="P31" s="75"/>
-      <c r="Q31" s="75"/>
-      <c r="R31" s="75"/>
-      <c r="S31" s="75"/>
-      <c r="T31" s="75"/>
-      <c r="U31" s="75"/>
-      <c r="V31" s="75"/>
-      <c r="W31" s="75"/>
-      <c r="X31" s="75"/>
-      <c r="Y31" s="75"/>
-      <c r="Z31" s="75"/>
-      <c r="AA31" s="75"/>
-      <c r="AB31" s="75"/>
-      <c r="AC31" s="75"/>
-      <c r="AD31" s="75"/>
-      <c r="AE31" s="75"/>
-      <c r="AF31" s="75"/>
-      <c r="AG31" s="74"/>
-      <c r="AH31" s="75"/>
-      <c r="AI31" s="75"/>
-      <c r="AJ31" s="75"/>
-      <c r="AK31" s="75"/>
-      <c r="AL31" s="75"/>
-      <c r="AM31" s="76"/>
-    </row>
-    <row r="32" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="57"/>
-      <c r="C32" s="38"/>
-      <c r="D32" s="77"/>
-      <c r="E32" s="78"/>
-      <c r="F32" s="78"/>
-      <c r="G32" s="78"/>
-      <c r="H32" s="78"/>
-      <c r="I32" s="78"/>
-      <c r="J32" s="78"/>
-      <c r="K32" s="79"/>
-      <c r="L32" s="78"/>
-      <c r="M32" s="78"/>
-      <c r="N32" s="78"/>
-      <c r="O32" s="78"/>
-      <c r="P32" s="78"/>
-      <c r="Q32" s="78"/>
-      <c r="R32" s="78"/>
-      <c r="S32" s="78"/>
-      <c r="T32" s="78"/>
-      <c r="U32" s="78"/>
-      <c r="V32" s="78"/>
-      <c r="W32" s="78"/>
-      <c r="X32" s="78"/>
-      <c r="Y32" s="78"/>
-      <c r="Z32" s="78"/>
-      <c r="AA32" s="78"/>
-      <c r="AB32" s="78"/>
-      <c r="AC32" s="78"/>
-      <c r="AD32" s="78"/>
-      <c r="AE32" s="78"/>
-      <c r="AF32" s="78"/>
-      <c r="AG32" s="77"/>
-      <c r="AH32" s="78"/>
-      <c r="AI32" s="78"/>
-      <c r="AJ32" s="78"/>
-      <c r="AK32" s="78"/>
-      <c r="AL32" s="78"/>
-      <c r="AM32" s="79"/>
-    </row>
-    <row r="33" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="60">
-        <v>6</v>
-      </c>
-      <c r="C33" s="61"/>
-      <c r="D33" s="74" t="s">
+      <c r="M41" s="75"/>
+      <c r="N41" s="75"/>
+      <c r="O41" s="75"/>
+      <c r="P41" s="75"/>
+      <c r="Q41" s="75"/>
+      <c r="R41" s="75"/>
+      <c r="S41" s="75"/>
+      <c r="T41" s="75"/>
+      <c r="U41" s="75"/>
+      <c r="V41" s="75"/>
+      <c r="W41" s="75"/>
+      <c r="X41" s="75"/>
+      <c r="Y41" s="75"/>
+      <c r="Z41" s="75"/>
+      <c r="AA41" s="75"/>
+      <c r="AB41" s="75"/>
+      <c r="AC41" s="75"/>
+      <c r="AD41" s="75"/>
+      <c r="AE41" s="75"/>
+      <c r="AF41" s="75"/>
+      <c r="AG41" s="74"/>
+      <c r="AH41" s="75"/>
+      <c r="AI41" s="75"/>
+      <c r="AJ41" s="75"/>
+      <c r="AK41" s="75"/>
+      <c r="AL41" s="75"/>
+      <c r="AM41" s="76"/>
+    </row>
+    <row r="42" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B42" s="57"/>
+      <c r="C42" s="38"/>
+      <c r="D42" s="77"/>
+      <c r="E42" s="78"/>
+      <c r="F42" s="78"/>
+      <c r="G42" s="78"/>
+      <c r="H42" s="78"/>
+      <c r="I42" s="78"/>
+      <c r="J42" s="78"/>
+      <c r="K42" s="79"/>
+      <c r="L42" s="78"/>
+      <c r="M42" s="78"/>
+      <c r="N42" s="78"/>
+      <c r="O42" s="78"/>
+      <c r="P42" s="78"/>
+      <c r="Q42" s="78"/>
+      <c r="R42" s="78"/>
+      <c r="S42" s="78"/>
+      <c r="T42" s="78"/>
+      <c r="U42" s="78"/>
+      <c r="V42" s="78"/>
+      <c r="W42" s="78"/>
+      <c r="X42" s="78"/>
+      <c r="Y42" s="78"/>
+      <c r="Z42" s="78"/>
+      <c r="AA42" s="78"/>
+      <c r="AB42" s="78"/>
+      <c r="AC42" s="78"/>
+      <c r="AD42" s="78"/>
+      <c r="AE42" s="78"/>
+      <c r="AF42" s="78"/>
+      <c r="AG42" s="77"/>
+      <c r="AH42" s="78"/>
+      <c r="AI42" s="78"/>
+      <c r="AJ42" s="78"/>
+      <c r="AK42" s="78"/>
+      <c r="AL42" s="78"/>
+      <c r="AM42" s="79"/>
+    </row>
+    <row r="43" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B43" s="60">
+        <v>7</v>
+      </c>
+      <c r="C43" s="61"/>
+      <c r="D43" s="74" t="s">
         <v>53</v>
       </c>
-      <c r="E33" s="75"/>
-      <c r="F33" s="75"/>
-      <c r="G33" s="75"/>
-      <c r="H33" s="75"/>
-      <c r="I33" s="75"/>
-      <c r="J33" s="75"/>
-      <c r="K33" s="76"/>
-      <c r="L33" s="75" t="s">
+      <c r="E43" s="75"/>
+      <c r="F43" s="75"/>
+      <c r="G43" s="75"/>
+      <c r="H43" s="75"/>
+      <c r="I43" s="75"/>
+      <c r="J43" s="75"/>
+      <c r="K43" s="76"/>
+      <c r="L43" s="75" t="s">
         <v>66</v>
       </c>
-      <c r="M33" s="75"/>
-      <c r="N33" s="75"/>
-      <c r="O33" s="75"/>
-      <c r="P33" s="75"/>
-      <c r="Q33" s="75"/>
-      <c r="R33" s="75"/>
-      <c r="S33" s="75"/>
-      <c r="T33" s="75"/>
-      <c r="U33" s="75"/>
-      <c r="V33" s="75"/>
-      <c r="W33" s="75"/>
-      <c r="X33" s="75"/>
-      <c r="Y33" s="75"/>
-      <c r="Z33" s="75"/>
-      <c r="AA33" s="75"/>
-      <c r="AB33" s="75"/>
-      <c r="AC33" s="75"/>
-      <c r="AD33" s="75"/>
-      <c r="AE33" s="75"/>
-      <c r="AF33" s="75"/>
-      <c r="AG33" s="74"/>
-      <c r="AH33" s="75"/>
-      <c r="AI33" s="75"/>
-      <c r="AJ33" s="75"/>
-      <c r="AK33" s="75"/>
-      <c r="AL33" s="75"/>
-      <c r="AM33" s="76"/>
-    </row>
-    <row r="34" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="57"/>
-      <c r="C34" s="38"/>
-      <c r="D34" s="77"/>
-      <c r="E34" s="78"/>
-      <c r="F34" s="78"/>
-      <c r="G34" s="78"/>
-      <c r="H34" s="78"/>
-      <c r="I34" s="78"/>
-      <c r="J34" s="78"/>
-      <c r="K34" s="79"/>
-      <c r="L34" s="78"/>
-      <c r="M34" s="78"/>
-      <c r="N34" s="78"/>
-      <c r="O34" s="78"/>
-      <c r="P34" s="78"/>
-      <c r="Q34" s="78"/>
-      <c r="R34" s="78"/>
-      <c r="S34" s="78"/>
-      <c r="T34" s="78"/>
-      <c r="U34" s="78"/>
-      <c r="V34" s="78"/>
-      <c r="W34" s="78"/>
-      <c r="X34" s="78"/>
-      <c r="Y34" s="78"/>
-      <c r="Z34" s="78"/>
-      <c r="AA34" s="78"/>
-      <c r="AB34" s="78"/>
-      <c r="AC34" s="78"/>
-      <c r="AD34" s="78"/>
-      <c r="AE34" s="78"/>
-      <c r="AF34" s="78"/>
-      <c r="AG34" s="77"/>
-      <c r="AH34" s="78"/>
-      <c r="AI34" s="78"/>
-      <c r="AJ34" s="78"/>
-      <c r="AK34" s="78"/>
-      <c r="AL34" s="78"/>
-      <c r="AM34" s="79"/>
-    </row>
-    <row r="35" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="36" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="37" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="38" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="39" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
+      <c r="M43" s="75"/>
+      <c r="N43" s="75"/>
+      <c r="O43" s="75"/>
+      <c r="P43" s="75"/>
+      <c r="Q43" s="75"/>
+      <c r="R43" s="75"/>
+      <c r="S43" s="75"/>
+      <c r="T43" s="75"/>
+      <c r="U43" s="75"/>
+      <c r="V43" s="75"/>
+      <c r="W43" s="75"/>
+      <c r="X43" s="75"/>
+      <c r="Y43" s="75"/>
+      <c r="Z43" s="75"/>
+      <c r="AA43" s="75"/>
+      <c r="AB43" s="75"/>
+      <c r="AC43" s="75"/>
+      <c r="AD43" s="75"/>
+      <c r="AE43" s="75"/>
+      <c r="AF43" s="75"/>
+      <c r="AG43" s="74"/>
+      <c r="AH43" s="75"/>
+      <c r="AI43" s="75"/>
+      <c r="AJ43" s="75"/>
+      <c r="AK43" s="75"/>
+      <c r="AL43" s="75"/>
+      <c r="AM43" s="76"/>
+    </row>
+    <row r="44" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B44" s="57"/>
+      <c r="C44" s="38"/>
+      <c r="D44" s="77"/>
+      <c r="E44" s="78"/>
+      <c r="F44" s="78"/>
+      <c r="G44" s="78"/>
+      <c r="H44" s="78"/>
+      <c r="I44" s="78"/>
+      <c r="J44" s="78"/>
+      <c r="K44" s="79"/>
+      <c r="L44" s="78"/>
+      <c r="M44" s="78"/>
+      <c r="N44" s="78"/>
+      <c r="O44" s="78"/>
+      <c r="P44" s="78"/>
+      <c r="Q44" s="78"/>
+      <c r="R44" s="78"/>
+      <c r="S44" s="78"/>
+      <c r="T44" s="78"/>
+      <c r="U44" s="78"/>
+      <c r="V44" s="78"/>
+      <c r="W44" s="78"/>
+      <c r="X44" s="78"/>
+      <c r="Y44" s="78"/>
+      <c r="Z44" s="78"/>
+      <c r="AA44" s="78"/>
+      <c r="AB44" s="78"/>
+      <c r="AC44" s="78"/>
+      <c r="AD44" s="78"/>
+      <c r="AE44" s="78"/>
+      <c r="AF44" s="78"/>
+      <c r="AG44" s="77"/>
+      <c r="AH44" s="78"/>
+      <c r="AI44" s="78"/>
+      <c r="AJ44" s="78"/>
+      <c r="AK44" s="78"/>
+      <c r="AL44" s="78"/>
+      <c r="AM44" s="79"/>
+    </row>
+    <row r="45" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="46" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="47" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="48" spans="2:39" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="49" ht="14.1" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:J3"/>
@@ -7272,7 +7706,7 @@
       </c>
       <c r="C6" s="45"/>
       <c r="D6" s="46" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E6" s="35"/>
       <c r="F6" s="35"/>
